--- a/strike_dip_import_template.xlsx
+++ b/strike_dip_import_template.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力テンプレート" sheetId="1" r:id="Rfc20bac7c7f14c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記入例・説明" sheetId="2" r:id="Refa358d3f2d542dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力テンプレート" sheetId="1" r:id="R6450cb6715954a53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記入例・説明" sheetId="2" r:id="Rb63361bee9914c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色定義" sheetId="3" r:id="Rb42e40b4a1c14125"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35,7 +36,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +63,21 @@
         <x:fgColor rgb="FFD9E6F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF315B7D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFDF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E6F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -70,7 +86,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="51">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -148,6 +164,44 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -360,587 +414,641 @@
     <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="38" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="38" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="10" t="str">
+      <x:c r="A1" s="37" t="str">
         <x:v>地点番号</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="37" t="str">
         <x:v>緯度</x:v>
       </x:c>
-      <x:c r="C1" s="10" t="str">
+      <x:c r="C1" s="37" t="str">
         <x:v>経度</x:v>
       </x:c>
-      <x:c r="D1" s="10" t="str">
+      <x:c r="D1" s="37" t="str">
         <x:v>走向</x:v>
       </x:c>
-      <x:c r="E1" s="10" t="str">
+      <x:c r="E1" s="37" t="str">
         <x:v>傾斜</x:v>
       </x:c>
-      <x:c r="F1" s="10" t="str">
+      <x:c r="F1" s="37" t="str">
         <x:v>測定日</x:v>
       </x:c>
-      <x:c r="G1" s="10" t="str">
+      <x:c r="G1" s="37" t="str">
         <x:v>岩種・地層名</x:v>
       </x:c>
-      <x:c r="H1" s="10" t="str">
+      <x:c r="H1" s="37" t="str">
         <x:v>面・構造</x:v>
       </x:c>
-      <x:c r="I1" s="10" t="str">
+      <x:c r="I1" s="37" t="str">
+        <x:v>色区分</x:v>
+      </x:c>
+      <x:c r="J1" s="37" t="str">
         <x:v>補足情報</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="18" t="str"/>
-      <x:c r="B2" s="19" t="str"/>
-      <x:c r="C2" s="19" t="str"/>
-      <x:c r="D2" s="18" t="str"/>
-      <x:c r="E2" s="18" t="str"/>
-      <x:c r="F2" s="20" t="str"/>
-      <x:c r="G2" s="18" t="str"/>
-      <x:c r="H2" s="18" t="str"/>
-      <x:c r="I2" s="18" t="str"/>
+      <x:c r="A2" s="42" t="str"/>
+      <x:c r="B2" s="43" t="str"/>
+      <x:c r="C2" s="43" t="str"/>
+      <x:c r="D2" s="42" t="str"/>
+      <x:c r="E2" s="42" t="str"/>
+      <x:c r="F2" s="44" t="str"/>
+      <x:c r="G2" s="42" t="str"/>
+      <x:c r="H2" s="42" t="str"/>
+      <x:c r="I2" s="42" t="str"/>
+      <x:c r="J2" s="42" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="18" t="str"/>
-      <x:c r="B3" s="19" t="str"/>
-      <x:c r="C3" s="19" t="str"/>
-      <x:c r="D3" s="18" t="str"/>
-      <x:c r="E3" s="18" t="str"/>
-      <x:c r="F3" s="20" t="str"/>
-      <x:c r="G3" s="18" t="str"/>
-      <x:c r="H3" s="18" t="str"/>
-      <x:c r="I3" s="18" t="str"/>
+      <x:c r="A3" s="42" t="str"/>
+      <x:c r="B3" s="43" t="str"/>
+      <x:c r="C3" s="43" t="str"/>
+      <x:c r="D3" s="42" t="str"/>
+      <x:c r="E3" s="42" t="str"/>
+      <x:c r="F3" s="44" t="str"/>
+      <x:c r="G3" s="42" t="str"/>
+      <x:c r="H3" s="42" t="str"/>
+      <x:c r="I3" s="42" t="str"/>
+      <x:c r="J3" s="42" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str"/>
-      <x:c r="B4" s="19" t="str"/>
-      <x:c r="C4" s="19" t="str"/>
-      <x:c r="D4" s="18" t="str"/>
-      <x:c r="E4" s="18" t="str"/>
-      <x:c r="F4" s="20" t="str"/>
-      <x:c r="G4" s="18" t="str"/>
-      <x:c r="H4" s="18" t="str"/>
-      <x:c r="I4" s="18" t="str"/>
+      <x:c r="A4" s="42" t="str"/>
+      <x:c r="B4" s="43" t="str"/>
+      <x:c r="C4" s="43" t="str"/>
+      <x:c r="D4" s="42" t="str"/>
+      <x:c r="E4" s="42" t="str"/>
+      <x:c r="F4" s="44" t="str"/>
+      <x:c r="G4" s="42" t="str"/>
+      <x:c r="H4" s="42" t="str"/>
+      <x:c r="I4" s="42" t="str"/>
+      <x:c r="J4" s="42" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str"/>
-      <x:c r="B5" s="19" t="str"/>
-      <x:c r="C5" s="19" t="str"/>
-      <x:c r="D5" s="18" t="str"/>
-      <x:c r="E5" s="18" t="str"/>
-      <x:c r="F5" s="20" t="str"/>
-      <x:c r="G5" s="18" t="str"/>
-      <x:c r="H5" s="18" t="str"/>
-      <x:c r="I5" s="18" t="str"/>
+      <x:c r="A5" s="42" t="str"/>
+      <x:c r="B5" s="43" t="str"/>
+      <x:c r="C5" s="43" t="str"/>
+      <x:c r="D5" s="42" t="str"/>
+      <x:c r="E5" s="42" t="str"/>
+      <x:c r="F5" s="44" t="str"/>
+      <x:c r="G5" s="42" t="str"/>
+      <x:c r="H5" s="42" t="str"/>
+      <x:c r="I5" s="42" t="str"/>
+      <x:c r="J5" s="42" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str"/>
-      <x:c r="B6" s="19" t="str"/>
-      <x:c r="C6" s="19" t="str"/>
-      <x:c r="D6" s="18" t="str"/>
-      <x:c r="E6" s="18" t="str"/>
-      <x:c r="F6" s="20" t="str"/>
-      <x:c r="G6" s="18" t="str"/>
-      <x:c r="H6" s="18" t="str"/>
-      <x:c r="I6" s="18" t="str"/>
+      <x:c r="A6" s="42" t="str"/>
+      <x:c r="B6" s="43" t="str"/>
+      <x:c r="C6" s="43" t="str"/>
+      <x:c r="D6" s="42" t="str"/>
+      <x:c r="E6" s="42" t="str"/>
+      <x:c r="F6" s="44" t="str"/>
+      <x:c r="G6" s="42" t="str"/>
+      <x:c r="H6" s="42" t="str"/>
+      <x:c r="I6" s="42" t="str"/>
+      <x:c r="J6" s="42" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str"/>
-      <x:c r="B7" s="19" t="str"/>
-      <x:c r="C7" s="19" t="str"/>
-      <x:c r="D7" s="18" t="str"/>
-      <x:c r="E7" s="18" t="str"/>
-      <x:c r="F7" s="20" t="str"/>
-      <x:c r="G7" s="18" t="str"/>
-      <x:c r="H7" s="18" t="str"/>
-      <x:c r="I7" s="18" t="str"/>
+      <x:c r="A7" s="42" t="str"/>
+      <x:c r="B7" s="43" t="str"/>
+      <x:c r="C7" s="43" t="str"/>
+      <x:c r="D7" s="42" t="str"/>
+      <x:c r="E7" s="42" t="str"/>
+      <x:c r="F7" s="44" t="str"/>
+      <x:c r="G7" s="42" t="str"/>
+      <x:c r="H7" s="42" t="str"/>
+      <x:c r="I7" s="42" t="str"/>
+      <x:c r="J7" s="42" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str"/>
-      <x:c r="B8" s="19" t="str"/>
-      <x:c r="C8" s="19" t="str"/>
-      <x:c r="D8" s="18" t="str"/>
-      <x:c r="E8" s="18" t="str"/>
-      <x:c r="F8" s="20" t="str"/>
-      <x:c r="G8" s="18" t="str"/>
-      <x:c r="H8" s="18" t="str"/>
-      <x:c r="I8" s="18" t="str"/>
+      <x:c r="A8" s="42" t="str"/>
+      <x:c r="B8" s="43" t="str"/>
+      <x:c r="C8" s="43" t="str"/>
+      <x:c r="D8" s="42" t="str"/>
+      <x:c r="E8" s="42" t="str"/>
+      <x:c r="F8" s="44" t="str"/>
+      <x:c r="G8" s="42" t="str"/>
+      <x:c r="H8" s="42" t="str"/>
+      <x:c r="I8" s="42" t="str"/>
+      <x:c r="J8" s="42" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str"/>
-      <x:c r="B9" s="19" t="str"/>
-      <x:c r="C9" s="19" t="str"/>
-      <x:c r="D9" s="18" t="str"/>
-      <x:c r="E9" s="18" t="str"/>
-      <x:c r="F9" s="20" t="str"/>
-      <x:c r="G9" s="18" t="str"/>
-      <x:c r="H9" s="18" t="str"/>
-      <x:c r="I9" s="18" t="str"/>
+      <x:c r="A9" s="42" t="str"/>
+      <x:c r="B9" s="43" t="str"/>
+      <x:c r="C9" s="43" t="str"/>
+      <x:c r="D9" s="42" t="str"/>
+      <x:c r="E9" s="42" t="str"/>
+      <x:c r="F9" s="44" t="str"/>
+      <x:c r="G9" s="42" t="str"/>
+      <x:c r="H9" s="42" t="str"/>
+      <x:c r="I9" s="42" t="str"/>
+      <x:c r="J9" s="42" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="str"/>
-      <x:c r="B10" s="19" t="str"/>
-      <x:c r="C10" s="19" t="str"/>
-      <x:c r="D10" s="18" t="str"/>
-      <x:c r="E10" s="18" t="str"/>
-      <x:c r="F10" s="20" t="str"/>
-      <x:c r="G10" s="18" t="str"/>
-      <x:c r="H10" s="18" t="str"/>
-      <x:c r="I10" s="18" t="str"/>
+      <x:c r="A10" s="42" t="str"/>
+      <x:c r="B10" s="43" t="str"/>
+      <x:c r="C10" s="43" t="str"/>
+      <x:c r="D10" s="42" t="str"/>
+      <x:c r="E10" s="42" t="str"/>
+      <x:c r="F10" s="44" t="str"/>
+      <x:c r="G10" s="42" t="str"/>
+      <x:c r="H10" s="42" t="str"/>
+      <x:c r="I10" s="42" t="str"/>
+      <x:c r="J10" s="42" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="18" t="str"/>
-      <x:c r="B11" s="19" t="str"/>
-      <x:c r="C11" s="19" t="str"/>
-      <x:c r="D11" s="18" t="str"/>
-      <x:c r="E11" s="18" t="str"/>
-      <x:c r="F11" s="20" t="str"/>
-      <x:c r="G11" s="18" t="str"/>
-      <x:c r="H11" s="18" t="str"/>
-      <x:c r="I11" s="18" t="str"/>
+      <x:c r="A11" s="42" t="str"/>
+      <x:c r="B11" s="43" t="str"/>
+      <x:c r="C11" s="43" t="str"/>
+      <x:c r="D11" s="42" t="str"/>
+      <x:c r="E11" s="42" t="str"/>
+      <x:c r="F11" s="44" t="str"/>
+      <x:c r="G11" s="42" t="str"/>
+      <x:c r="H11" s="42" t="str"/>
+      <x:c r="I11" s="42" t="str"/>
+      <x:c r="J11" s="42" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="18" t="str"/>
-      <x:c r="B12" s="19" t="str"/>
-      <x:c r="C12" s="19" t="str"/>
-      <x:c r="D12" s="18" t="str"/>
-      <x:c r="E12" s="18" t="str"/>
-      <x:c r="F12" s="20" t="str"/>
-      <x:c r="G12" s="18" t="str"/>
-      <x:c r="H12" s="18" t="str"/>
-      <x:c r="I12" s="18" t="str"/>
+      <x:c r="A12" s="42" t="str"/>
+      <x:c r="B12" s="43" t="str"/>
+      <x:c r="C12" s="43" t="str"/>
+      <x:c r="D12" s="42" t="str"/>
+      <x:c r="E12" s="42" t="str"/>
+      <x:c r="F12" s="44" t="str"/>
+      <x:c r="G12" s="42" t="str"/>
+      <x:c r="H12" s="42" t="str"/>
+      <x:c r="I12" s="42" t="str"/>
+      <x:c r="J12" s="42" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="18" t="str"/>
-      <x:c r="B13" s="19" t="str"/>
-      <x:c r="C13" s="19" t="str"/>
-      <x:c r="D13" s="18" t="str"/>
-      <x:c r="E13" s="18" t="str"/>
-      <x:c r="F13" s="20" t="str"/>
-      <x:c r="G13" s="18" t="str"/>
-      <x:c r="H13" s="18" t="str"/>
-      <x:c r="I13" s="18" t="str"/>
+      <x:c r="A13" s="42" t="str"/>
+      <x:c r="B13" s="43" t="str"/>
+      <x:c r="C13" s="43" t="str"/>
+      <x:c r="D13" s="42" t="str"/>
+      <x:c r="E13" s="42" t="str"/>
+      <x:c r="F13" s="44" t="str"/>
+      <x:c r="G13" s="42" t="str"/>
+      <x:c r="H13" s="42" t="str"/>
+      <x:c r="I13" s="42" t="str"/>
+      <x:c r="J13" s="42" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="18" t="str"/>
-      <x:c r="B14" s="19" t="str"/>
-      <x:c r="C14" s="19" t="str"/>
-      <x:c r="D14" s="18" t="str"/>
-      <x:c r="E14" s="18" t="str"/>
-      <x:c r="F14" s="20" t="str"/>
-      <x:c r="G14" s="18" t="str"/>
-      <x:c r="H14" s="18" t="str"/>
-      <x:c r="I14" s="18" t="str"/>
+      <x:c r="A14" s="42" t="str"/>
+      <x:c r="B14" s="43" t="str"/>
+      <x:c r="C14" s="43" t="str"/>
+      <x:c r="D14" s="42" t="str"/>
+      <x:c r="E14" s="42" t="str"/>
+      <x:c r="F14" s="44" t="str"/>
+      <x:c r="G14" s="42" t="str"/>
+      <x:c r="H14" s="42" t="str"/>
+      <x:c r="I14" s="42" t="str"/>
+      <x:c r="J14" s="42" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="18" t="str"/>
-      <x:c r="B15" s="19" t="str"/>
-      <x:c r="C15" s="19" t="str"/>
-      <x:c r="D15" s="18" t="str"/>
-      <x:c r="E15" s="18" t="str"/>
-      <x:c r="F15" s="20" t="str"/>
-      <x:c r="G15" s="18" t="str"/>
-      <x:c r="H15" s="18" t="str"/>
-      <x:c r="I15" s="18" t="str"/>
+      <x:c r="A15" s="42" t="str"/>
+      <x:c r="B15" s="43" t="str"/>
+      <x:c r="C15" s="43" t="str"/>
+      <x:c r="D15" s="42" t="str"/>
+      <x:c r="E15" s="42" t="str"/>
+      <x:c r="F15" s="44" t="str"/>
+      <x:c r="G15" s="42" t="str"/>
+      <x:c r="H15" s="42" t="str"/>
+      <x:c r="I15" s="42" t="str"/>
+      <x:c r="J15" s="42" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="18" t="str"/>
-      <x:c r="B16" s="19" t="str"/>
-      <x:c r="C16" s="19" t="str"/>
-      <x:c r="D16" s="18" t="str"/>
-      <x:c r="E16" s="18" t="str"/>
-      <x:c r="F16" s="20" t="str"/>
-      <x:c r="G16" s="18" t="str"/>
-      <x:c r="H16" s="18" t="str"/>
-      <x:c r="I16" s="18" t="str"/>
+      <x:c r="A16" s="42" t="str"/>
+      <x:c r="B16" s="43" t="str"/>
+      <x:c r="C16" s="43" t="str"/>
+      <x:c r="D16" s="42" t="str"/>
+      <x:c r="E16" s="42" t="str"/>
+      <x:c r="F16" s="44" t="str"/>
+      <x:c r="G16" s="42" t="str"/>
+      <x:c r="H16" s="42" t="str"/>
+      <x:c r="I16" s="42" t="str"/>
+      <x:c r="J16" s="42" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="18" t="str"/>
-      <x:c r="B17" s="19" t="str"/>
-      <x:c r="C17" s="19" t="str"/>
-      <x:c r="D17" s="18" t="str"/>
-      <x:c r="E17" s="18" t="str"/>
-      <x:c r="F17" s="20" t="str"/>
-      <x:c r="G17" s="18" t="str"/>
-      <x:c r="H17" s="18" t="str"/>
-      <x:c r="I17" s="18" t="str"/>
+      <x:c r="A17" s="42" t="str"/>
+      <x:c r="B17" s="43" t="str"/>
+      <x:c r="C17" s="43" t="str"/>
+      <x:c r="D17" s="42" t="str"/>
+      <x:c r="E17" s="42" t="str"/>
+      <x:c r="F17" s="44" t="str"/>
+      <x:c r="G17" s="42" t="str"/>
+      <x:c r="H17" s="42" t="str"/>
+      <x:c r="I17" s="42" t="str"/>
+      <x:c r="J17" s="42" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="18" t="str"/>
-      <x:c r="B18" s="19" t="str"/>
-      <x:c r="C18" s="19" t="str"/>
-      <x:c r="D18" s="18" t="str"/>
-      <x:c r="E18" s="18" t="str"/>
-      <x:c r="F18" s="20" t="str"/>
-      <x:c r="G18" s="18" t="str"/>
-      <x:c r="H18" s="18" t="str"/>
-      <x:c r="I18" s="18" t="str"/>
+      <x:c r="A18" s="42" t="str"/>
+      <x:c r="B18" s="43" t="str"/>
+      <x:c r="C18" s="43" t="str"/>
+      <x:c r="D18" s="42" t="str"/>
+      <x:c r="E18" s="42" t="str"/>
+      <x:c r="F18" s="44" t="str"/>
+      <x:c r="G18" s="42" t="str"/>
+      <x:c r="H18" s="42" t="str"/>
+      <x:c r="I18" s="42" t="str"/>
+      <x:c r="J18" s="42" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="18" t="str"/>
-      <x:c r="B19" s="19" t="str"/>
-      <x:c r="C19" s="19" t="str"/>
-      <x:c r="D19" s="18" t="str"/>
-      <x:c r="E19" s="18" t="str"/>
-      <x:c r="F19" s="20" t="str"/>
-      <x:c r="G19" s="18" t="str"/>
-      <x:c r="H19" s="18" t="str"/>
-      <x:c r="I19" s="18" t="str"/>
+      <x:c r="A19" s="42" t="str"/>
+      <x:c r="B19" s="43" t="str"/>
+      <x:c r="C19" s="43" t="str"/>
+      <x:c r="D19" s="42" t="str"/>
+      <x:c r="E19" s="42" t="str"/>
+      <x:c r="F19" s="44" t="str"/>
+      <x:c r="G19" s="42" t="str"/>
+      <x:c r="H19" s="42" t="str"/>
+      <x:c r="I19" s="42" t="str"/>
+      <x:c r="J19" s="42" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="18" t="str"/>
-      <x:c r="B20" s="19" t="str"/>
-      <x:c r="C20" s="19" t="str"/>
-      <x:c r="D20" s="18" t="str"/>
-      <x:c r="E20" s="18" t="str"/>
-      <x:c r="F20" s="20" t="str"/>
-      <x:c r="G20" s="18" t="str"/>
-      <x:c r="H20" s="18" t="str"/>
-      <x:c r="I20" s="18" t="str"/>
+      <x:c r="A20" s="42" t="str"/>
+      <x:c r="B20" s="43" t="str"/>
+      <x:c r="C20" s="43" t="str"/>
+      <x:c r="D20" s="42" t="str"/>
+      <x:c r="E20" s="42" t="str"/>
+      <x:c r="F20" s="44" t="str"/>
+      <x:c r="G20" s="42" t="str"/>
+      <x:c r="H20" s="42" t="str"/>
+      <x:c r="I20" s="42" t="str"/>
+      <x:c r="J20" s="42" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="18" t="str"/>
-      <x:c r="B21" s="19" t="str"/>
-      <x:c r="C21" s="19" t="str"/>
-      <x:c r="D21" s="18" t="str"/>
-      <x:c r="E21" s="18" t="str"/>
-      <x:c r="F21" s="20" t="str"/>
-      <x:c r="G21" s="18" t="str"/>
-      <x:c r="H21" s="18" t="str"/>
-      <x:c r="I21" s="18" t="str"/>
+      <x:c r="A21" s="42" t="str"/>
+      <x:c r="B21" s="43" t="str"/>
+      <x:c r="C21" s="43" t="str"/>
+      <x:c r="D21" s="42" t="str"/>
+      <x:c r="E21" s="42" t="str"/>
+      <x:c r="F21" s="44" t="str"/>
+      <x:c r="G21" s="42" t="str"/>
+      <x:c r="H21" s="42" t="str"/>
+      <x:c r="I21" s="42" t="str"/>
+      <x:c r="J21" s="42" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="18" t="str"/>
-      <x:c r="B22" s="19" t="str"/>
-      <x:c r="C22" s="19" t="str"/>
-      <x:c r="D22" s="18" t="str"/>
-      <x:c r="E22" s="18" t="str"/>
-      <x:c r="F22" s="20" t="str"/>
-      <x:c r="G22" s="18" t="str"/>
-      <x:c r="H22" s="18" t="str"/>
-      <x:c r="I22" s="18" t="str"/>
+      <x:c r="A22" s="42" t="str"/>
+      <x:c r="B22" s="43" t="str"/>
+      <x:c r="C22" s="43" t="str"/>
+      <x:c r="D22" s="42" t="str"/>
+      <x:c r="E22" s="42" t="str"/>
+      <x:c r="F22" s="44" t="str"/>
+      <x:c r="G22" s="42" t="str"/>
+      <x:c r="H22" s="42" t="str"/>
+      <x:c r="I22" s="42" t="str"/>
+      <x:c r="J22" s="42" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="18" t="str"/>
-      <x:c r="B23" s="19" t="str"/>
-      <x:c r="C23" s="19" t="str"/>
-      <x:c r="D23" s="18" t="str"/>
-      <x:c r="E23" s="18" t="str"/>
-      <x:c r="F23" s="20" t="str"/>
-      <x:c r="G23" s="18" t="str"/>
-      <x:c r="H23" s="18" t="str"/>
-      <x:c r="I23" s="18" t="str"/>
+      <x:c r="A23" s="42" t="str"/>
+      <x:c r="B23" s="43" t="str"/>
+      <x:c r="C23" s="43" t="str"/>
+      <x:c r="D23" s="42" t="str"/>
+      <x:c r="E23" s="42" t="str"/>
+      <x:c r="F23" s="44" t="str"/>
+      <x:c r="G23" s="42" t="str"/>
+      <x:c r="H23" s="42" t="str"/>
+      <x:c r="I23" s="42" t="str"/>
+      <x:c r="J23" s="42" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="18" t="str"/>
-      <x:c r="B24" s="19" t="str"/>
-      <x:c r="C24" s="19" t="str"/>
-      <x:c r="D24" s="18" t="str"/>
-      <x:c r="E24" s="18" t="str"/>
-      <x:c r="F24" s="20" t="str"/>
-      <x:c r="G24" s="18" t="str"/>
-      <x:c r="H24" s="18" t="str"/>
-      <x:c r="I24" s="18" t="str"/>
+      <x:c r="A24" s="42" t="str"/>
+      <x:c r="B24" s="43" t="str"/>
+      <x:c r="C24" s="43" t="str"/>
+      <x:c r="D24" s="42" t="str"/>
+      <x:c r="E24" s="42" t="str"/>
+      <x:c r="F24" s="44" t="str"/>
+      <x:c r="G24" s="42" t="str"/>
+      <x:c r="H24" s="42" t="str"/>
+      <x:c r="I24" s="42" t="str"/>
+      <x:c r="J24" s="42" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="18" t="str"/>
-      <x:c r="B25" s="19" t="str"/>
-      <x:c r="C25" s="19" t="str"/>
-      <x:c r="D25" s="18" t="str"/>
-      <x:c r="E25" s="18" t="str"/>
-      <x:c r="F25" s="20" t="str"/>
-      <x:c r="G25" s="18" t="str"/>
-      <x:c r="H25" s="18" t="str"/>
-      <x:c r="I25" s="18" t="str"/>
+      <x:c r="A25" s="42" t="str"/>
+      <x:c r="B25" s="43" t="str"/>
+      <x:c r="C25" s="43" t="str"/>
+      <x:c r="D25" s="42" t="str"/>
+      <x:c r="E25" s="42" t="str"/>
+      <x:c r="F25" s="44" t="str"/>
+      <x:c r="G25" s="42" t="str"/>
+      <x:c r="H25" s="42" t="str"/>
+      <x:c r="I25" s="42" t="str"/>
+      <x:c r="J25" s="42" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="18" t="str"/>
-      <x:c r="B26" s="19" t="str"/>
-      <x:c r="C26" s="19" t="str"/>
-      <x:c r="D26" s="18" t="str"/>
-      <x:c r="E26" s="18" t="str"/>
-      <x:c r="F26" s="20" t="str"/>
-      <x:c r="G26" s="18" t="str"/>
-      <x:c r="H26" s="18" t="str"/>
-      <x:c r="I26" s="18" t="str"/>
+      <x:c r="A26" s="42" t="str"/>
+      <x:c r="B26" s="43" t="str"/>
+      <x:c r="C26" s="43" t="str"/>
+      <x:c r="D26" s="42" t="str"/>
+      <x:c r="E26" s="42" t="str"/>
+      <x:c r="F26" s="44" t="str"/>
+      <x:c r="G26" s="42" t="str"/>
+      <x:c r="H26" s="42" t="str"/>
+      <x:c r="I26" s="42" t="str"/>
+      <x:c r="J26" s="42" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="18" t="str"/>
-      <x:c r="B27" s="19" t="str"/>
-      <x:c r="C27" s="19" t="str"/>
-      <x:c r="D27" s="18" t="str"/>
-      <x:c r="E27" s="18" t="str"/>
-      <x:c r="F27" s="20" t="str"/>
-      <x:c r="G27" s="18" t="str"/>
-      <x:c r="H27" s="18" t="str"/>
-      <x:c r="I27" s="18" t="str"/>
+      <x:c r="A27" s="42" t="str"/>
+      <x:c r="B27" s="43" t="str"/>
+      <x:c r="C27" s="43" t="str"/>
+      <x:c r="D27" s="42" t="str"/>
+      <x:c r="E27" s="42" t="str"/>
+      <x:c r="F27" s="44" t="str"/>
+      <x:c r="G27" s="42" t="str"/>
+      <x:c r="H27" s="42" t="str"/>
+      <x:c r="I27" s="42" t="str"/>
+      <x:c r="J27" s="42" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="18" t="str"/>
-      <x:c r="B28" s="19" t="str"/>
-      <x:c r="C28" s="19" t="str"/>
-      <x:c r="D28" s="18" t="str"/>
-      <x:c r="E28" s="18" t="str"/>
-      <x:c r="F28" s="20" t="str"/>
-      <x:c r="G28" s="18" t="str"/>
-      <x:c r="H28" s="18" t="str"/>
-      <x:c r="I28" s="18" t="str"/>
+      <x:c r="A28" s="42" t="str"/>
+      <x:c r="B28" s="43" t="str"/>
+      <x:c r="C28" s="43" t="str"/>
+      <x:c r="D28" s="42" t="str"/>
+      <x:c r="E28" s="42" t="str"/>
+      <x:c r="F28" s="44" t="str"/>
+      <x:c r="G28" s="42" t="str"/>
+      <x:c r="H28" s="42" t="str"/>
+      <x:c r="I28" s="42" t="str"/>
+      <x:c r="J28" s="42" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="18" t="str"/>
-      <x:c r="B29" s="19" t="str"/>
-      <x:c r="C29" s="19" t="str"/>
-      <x:c r="D29" s="18" t="str"/>
-      <x:c r="E29" s="18" t="str"/>
-      <x:c r="F29" s="20" t="str"/>
-      <x:c r="G29" s="18" t="str"/>
-      <x:c r="H29" s="18" t="str"/>
-      <x:c r="I29" s="18" t="str"/>
+      <x:c r="A29" s="42" t="str"/>
+      <x:c r="B29" s="43" t="str"/>
+      <x:c r="C29" s="43" t="str"/>
+      <x:c r="D29" s="42" t="str"/>
+      <x:c r="E29" s="42" t="str"/>
+      <x:c r="F29" s="44" t="str"/>
+      <x:c r="G29" s="42" t="str"/>
+      <x:c r="H29" s="42" t="str"/>
+      <x:c r="I29" s="42" t="str"/>
+      <x:c r="J29" s="42" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="18" t="str"/>
-      <x:c r="B30" s="19" t="str"/>
-      <x:c r="C30" s="19" t="str"/>
-      <x:c r="D30" s="18" t="str"/>
-      <x:c r="E30" s="18" t="str"/>
-      <x:c r="F30" s="20" t="str"/>
-      <x:c r="G30" s="18" t="str"/>
-      <x:c r="H30" s="18" t="str"/>
-      <x:c r="I30" s="18" t="str"/>
+      <x:c r="A30" s="42" t="str"/>
+      <x:c r="B30" s="43" t="str"/>
+      <x:c r="C30" s="43" t="str"/>
+      <x:c r="D30" s="42" t="str"/>
+      <x:c r="E30" s="42" t="str"/>
+      <x:c r="F30" s="44" t="str"/>
+      <x:c r="G30" s="42" t="str"/>
+      <x:c r="H30" s="42" t="str"/>
+      <x:c r="I30" s="42" t="str"/>
+      <x:c r="J30" s="42" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="18" t="str"/>
-      <x:c r="B31" s="19" t="str"/>
-      <x:c r="C31" s="19" t="str"/>
-      <x:c r="D31" s="18" t="str"/>
-      <x:c r="E31" s="18" t="str"/>
-      <x:c r="F31" s="20" t="str"/>
-      <x:c r="G31" s="18" t="str"/>
-      <x:c r="H31" s="18" t="str"/>
-      <x:c r="I31" s="18" t="str"/>
+      <x:c r="A31" s="42" t="str"/>
+      <x:c r="B31" s="43" t="str"/>
+      <x:c r="C31" s="43" t="str"/>
+      <x:c r="D31" s="42" t="str"/>
+      <x:c r="E31" s="42" t="str"/>
+      <x:c r="F31" s="44" t="str"/>
+      <x:c r="G31" s="42" t="str"/>
+      <x:c r="H31" s="42" t="str"/>
+      <x:c r="I31" s="42" t="str"/>
+      <x:c r="J31" s="42" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="18" t="str"/>
-      <x:c r="B32" s="19" t="str"/>
-      <x:c r="C32" s="19" t="str"/>
-      <x:c r="D32" s="18" t="str"/>
-      <x:c r="E32" s="18" t="str"/>
-      <x:c r="F32" s="20" t="str"/>
-      <x:c r="G32" s="18" t="str"/>
-      <x:c r="H32" s="18" t="str"/>
-      <x:c r="I32" s="18" t="str"/>
+      <x:c r="A32" s="42" t="str"/>
+      <x:c r="B32" s="43" t="str"/>
+      <x:c r="C32" s="43" t="str"/>
+      <x:c r="D32" s="42" t="str"/>
+      <x:c r="E32" s="42" t="str"/>
+      <x:c r="F32" s="44" t="str"/>
+      <x:c r="G32" s="42" t="str"/>
+      <x:c r="H32" s="42" t="str"/>
+      <x:c r="I32" s="42" t="str"/>
+      <x:c r="J32" s="42" t="str"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="18" t="str"/>
-      <x:c r="B33" s="19" t="str"/>
-      <x:c r="C33" s="19" t="str"/>
-      <x:c r="D33" s="18" t="str"/>
-      <x:c r="E33" s="18" t="str"/>
-      <x:c r="F33" s="20" t="str"/>
-      <x:c r="G33" s="18" t="str"/>
-      <x:c r="H33" s="18" t="str"/>
-      <x:c r="I33" s="18" t="str"/>
+      <x:c r="A33" s="42" t="str"/>
+      <x:c r="B33" s="43" t="str"/>
+      <x:c r="C33" s="43" t="str"/>
+      <x:c r="D33" s="42" t="str"/>
+      <x:c r="E33" s="42" t="str"/>
+      <x:c r="F33" s="44" t="str"/>
+      <x:c r="G33" s="42" t="str"/>
+      <x:c r="H33" s="42" t="str"/>
+      <x:c r="I33" s="42" t="str"/>
+      <x:c r="J33" s="42" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="18" t="str"/>
-      <x:c r="B34" s="19" t="str"/>
-      <x:c r="C34" s="19" t="str"/>
-      <x:c r="D34" s="18" t="str"/>
-      <x:c r="E34" s="18" t="str"/>
-      <x:c r="F34" s="20" t="str"/>
-      <x:c r="G34" s="18" t="str"/>
-      <x:c r="H34" s="18" t="str"/>
-      <x:c r="I34" s="18" t="str"/>
+      <x:c r="A34" s="42" t="str"/>
+      <x:c r="B34" s="43" t="str"/>
+      <x:c r="C34" s="43" t="str"/>
+      <x:c r="D34" s="42" t="str"/>
+      <x:c r="E34" s="42" t="str"/>
+      <x:c r="F34" s="44" t="str"/>
+      <x:c r="G34" s="42" t="str"/>
+      <x:c r="H34" s="42" t="str"/>
+      <x:c r="I34" s="42" t="str"/>
+      <x:c r="J34" s="42" t="str"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="18" t="str"/>
-      <x:c r="B35" s="19" t="str"/>
-      <x:c r="C35" s="19" t="str"/>
-      <x:c r="D35" s="18" t="str"/>
-      <x:c r="E35" s="18" t="str"/>
-      <x:c r="F35" s="20" t="str"/>
-      <x:c r="G35" s="18" t="str"/>
-      <x:c r="H35" s="18" t="str"/>
-      <x:c r="I35" s="18" t="str"/>
+      <x:c r="A35" s="42" t="str"/>
+      <x:c r="B35" s="43" t="str"/>
+      <x:c r="C35" s="43" t="str"/>
+      <x:c r="D35" s="42" t="str"/>
+      <x:c r="E35" s="42" t="str"/>
+      <x:c r="F35" s="44" t="str"/>
+      <x:c r="G35" s="42" t="str"/>
+      <x:c r="H35" s="42" t="str"/>
+      <x:c r="I35" s="42" t="str"/>
+      <x:c r="J35" s="42" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="18" t="str"/>
-      <x:c r="B36" s="19" t="str"/>
-      <x:c r="C36" s="19" t="str"/>
-      <x:c r="D36" s="18" t="str"/>
-      <x:c r="E36" s="18" t="str"/>
-      <x:c r="F36" s="20" t="str"/>
-      <x:c r="G36" s="18" t="str"/>
-      <x:c r="H36" s="18" t="str"/>
-      <x:c r="I36" s="18" t="str"/>
+      <x:c r="A36" s="42" t="str"/>
+      <x:c r="B36" s="43" t="str"/>
+      <x:c r="C36" s="43" t="str"/>
+      <x:c r="D36" s="42" t="str"/>
+      <x:c r="E36" s="42" t="str"/>
+      <x:c r="F36" s="44" t="str"/>
+      <x:c r="G36" s="42" t="str"/>
+      <x:c r="H36" s="42" t="str"/>
+      <x:c r="I36" s="42" t="str"/>
+      <x:c r="J36" s="42" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="18" t="str"/>
-      <x:c r="B37" s="19" t="str"/>
-      <x:c r="C37" s="19" t="str"/>
-      <x:c r="D37" s="18" t="str"/>
-      <x:c r="E37" s="18" t="str"/>
-      <x:c r="F37" s="20" t="str"/>
-      <x:c r="G37" s="18" t="str"/>
-      <x:c r="H37" s="18" t="str"/>
-      <x:c r="I37" s="18" t="str"/>
+      <x:c r="A37" s="42" t="str"/>
+      <x:c r="B37" s="43" t="str"/>
+      <x:c r="C37" s="43" t="str"/>
+      <x:c r="D37" s="42" t="str"/>
+      <x:c r="E37" s="42" t="str"/>
+      <x:c r="F37" s="44" t="str"/>
+      <x:c r="G37" s="42" t="str"/>
+      <x:c r="H37" s="42" t="str"/>
+      <x:c r="I37" s="42" t="str"/>
+      <x:c r="J37" s="42" t="str"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="18" t="str"/>
-      <x:c r="B38" s="19" t="str"/>
-      <x:c r="C38" s="19" t="str"/>
-      <x:c r="D38" s="18" t="str"/>
-      <x:c r="E38" s="18" t="str"/>
-      <x:c r="F38" s="20" t="str"/>
-      <x:c r="G38" s="18" t="str"/>
-      <x:c r="H38" s="18" t="str"/>
-      <x:c r="I38" s="18" t="str"/>
+      <x:c r="A38" s="42" t="str"/>
+      <x:c r="B38" s="43" t="str"/>
+      <x:c r="C38" s="43" t="str"/>
+      <x:c r="D38" s="42" t="str"/>
+      <x:c r="E38" s="42" t="str"/>
+      <x:c r="F38" s="44" t="str"/>
+      <x:c r="G38" s="42" t="str"/>
+      <x:c r="H38" s="42" t="str"/>
+      <x:c r="I38" s="42" t="str"/>
+      <x:c r="J38" s="42" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="18" t="str"/>
-      <x:c r="B39" s="19" t="str"/>
-      <x:c r="C39" s="19" t="str"/>
-      <x:c r="D39" s="18" t="str"/>
-      <x:c r="E39" s="18" t="str"/>
-      <x:c r="F39" s="20" t="str"/>
-      <x:c r="G39" s="18" t="str"/>
-      <x:c r="H39" s="18" t="str"/>
-      <x:c r="I39" s="18" t="str"/>
+      <x:c r="A39" s="42" t="str"/>
+      <x:c r="B39" s="43" t="str"/>
+      <x:c r="C39" s="43" t="str"/>
+      <x:c r="D39" s="42" t="str"/>
+      <x:c r="E39" s="42" t="str"/>
+      <x:c r="F39" s="44" t="str"/>
+      <x:c r="G39" s="42" t="str"/>
+      <x:c r="H39" s="42" t="str"/>
+      <x:c r="I39" s="42" t="str"/>
+      <x:c r="J39" s="42" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="18" t="str"/>
-      <x:c r="B40" s="19" t="str"/>
-      <x:c r="C40" s="19" t="str"/>
-      <x:c r="D40" s="18" t="str"/>
-      <x:c r="E40" s="18" t="str"/>
-      <x:c r="F40" s="20" t="str"/>
-      <x:c r="G40" s="18" t="str"/>
-      <x:c r="H40" s="18" t="str"/>
-      <x:c r="I40" s="18" t="str"/>
+      <x:c r="A40" s="42" t="str"/>
+      <x:c r="B40" s="43" t="str"/>
+      <x:c r="C40" s="43" t="str"/>
+      <x:c r="D40" s="42" t="str"/>
+      <x:c r="E40" s="42" t="str"/>
+      <x:c r="F40" s="44" t="str"/>
+      <x:c r="G40" s="42" t="str"/>
+      <x:c r="H40" s="42" t="str"/>
+      <x:c r="I40" s="42" t="str"/>
+      <x:c r="J40" s="42" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="18" t="str"/>
-      <x:c r="B41" s="19" t="str"/>
-      <x:c r="C41" s="19" t="str"/>
-      <x:c r="D41" s="18" t="str"/>
-      <x:c r="E41" s="18" t="str"/>
-      <x:c r="F41" s="20" t="str"/>
-      <x:c r="G41" s="18" t="str"/>
-      <x:c r="H41" s="18" t="str"/>
-      <x:c r="I41" s="18" t="str"/>
+      <x:c r="A41" s="42" t="str"/>
+      <x:c r="B41" s="43" t="str"/>
+      <x:c r="C41" s="43" t="str"/>
+      <x:c r="D41" s="42" t="str"/>
+      <x:c r="E41" s="42" t="str"/>
+      <x:c r="F41" s="44" t="str"/>
+      <x:c r="G41" s="42" t="str"/>
+      <x:c r="H41" s="42" t="str"/>
+      <x:c r="I41" s="42" t="str"/>
+      <x:c r="J41" s="42" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="18" t="str"/>
-      <x:c r="B42" s="19" t="str"/>
-      <x:c r="C42" s="19" t="str"/>
-      <x:c r="D42" s="18" t="str"/>
-      <x:c r="E42" s="18" t="str"/>
-      <x:c r="F42" s="20" t="str"/>
-      <x:c r="G42" s="18" t="str"/>
-      <x:c r="H42" s="18" t="str"/>
-      <x:c r="I42" s="18" t="str"/>
+      <x:c r="A42" s="42" t="str"/>
+      <x:c r="B42" s="43" t="str"/>
+      <x:c r="C42" s="43" t="str"/>
+      <x:c r="D42" s="42" t="str"/>
+      <x:c r="E42" s="42" t="str"/>
+      <x:c r="F42" s="44" t="str"/>
+      <x:c r="G42" s="42" t="str"/>
+      <x:c r="H42" s="42" t="str"/>
+      <x:c r="I42" s="42" t="str"/>
+      <x:c r="J42" s="42" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="18" t="str"/>
-      <x:c r="B43" s="19" t="str"/>
-      <x:c r="C43" s="19" t="str"/>
-      <x:c r="D43" s="18" t="str"/>
-      <x:c r="E43" s="18" t="str"/>
-      <x:c r="F43" s="20" t="str"/>
-      <x:c r="G43" s="18" t="str"/>
-      <x:c r="H43" s="18" t="str"/>
-      <x:c r="I43" s="18" t="str"/>
+      <x:c r="A43" s="42" t="str"/>
+      <x:c r="B43" s="43" t="str"/>
+      <x:c r="C43" s="43" t="str"/>
+      <x:c r="D43" s="42" t="str"/>
+      <x:c r="E43" s="42" t="str"/>
+      <x:c r="F43" s="44" t="str"/>
+      <x:c r="G43" s="42" t="str"/>
+      <x:c r="H43" s="42" t="str"/>
+      <x:c r="I43" s="42" t="str"/>
+      <x:c r="J43" s="42" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="18" t="str"/>
-      <x:c r="B44" s="19" t="str"/>
-      <x:c r="C44" s="19" t="str"/>
-      <x:c r="D44" s="18" t="str"/>
-      <x:c r="E44" s="18" t="str"/>
-      <x:c r="F44" s="20" t="str"/>
-      <x:c r="G44" s="18" t="str"/>
-      <x:c r="H44" s="18" t="str"/>
-      <x:c r="I44" s="18" t="str"/>
+      <x:c r="A44" s="42" t="str"/>
+      <x:c r="B44" s="43" t="str"/>
+      <x:c r="C44" s="43" t="str"/>
+      <x:c r="D44" s="42" t="str"/>
+      <x:c r="E44" s="42" t="str"/>
+      <x:c r="F44" s="44" t="str"/>
+      <x:c r="G44" s="42" t="str"/>
+      <x:c r="H44" s="42" t="str"/>
+      <x:c r="I44" s="42" t="str"/>
+      <x:c r="J44" s="42" t="str"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="18" t="str"/>
-      <x:c r="B45" s="19" t="str"/>
-      <x:c r="C45" s="19" t="str"/>
-      <x:c r="D45" s="18" t="str"/>
-      <x:c r="E45" s="18" t="str"/>
-      <x:c r="F45" s="20" t="str"/>
-      <x:c r="G45" s="18" t="str"/>
-      <x:c r="H45" s="18" t="str"/>
-      <x:c r="I45" s="18" t="str"/>
+      <x:c r="A45" s="42" t="str"/>
+      <x:c r="B45" s="43" t="str"/>
+      <x:c r="C45" s="43" t="str"/>
+      <x:c r="D45" s="42" t="str"/>
+      <x:c r="E45" s="42" t="str"/>
+      <x:c r="F45" s="44" t="str"/>
+      <x:c r="G45" s="42" t="str"/>
+      <x:c r="H45" s="42" t="str"/>
+      <x:c r="I45" s="42" t="str"/>
+      <x:c r="J45" s="42" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="18" t="str"/>
-      <x:c r="B46" s="19" t="str"/>
-      <x:c r="C46" s="19" t="str"/>
-      <x:c r="D46" s="18" t="str"/>
-      <x:c r="E46" s="18" t="str"/>
-      <x:c r="F46" s="20" t="str"/>
-      <x:c r="G46" s="18" t="str"/>
-      <x:c r="H46" s="18" t="str"/>
-      <x:c r="I46" s="18" t="str"/>
+      <x:c r="A46" s="42" t="str"/>
+      <x:c r="B46" s="43" t="str"/>
+      <x:c r="C46" s="43" t="str"/>
+      <x:c r="D46" s="42" t="str"/>
+      <x:c r="E46" s="42" t="str"/>
+      <x:c r="F46" s="44" t="str"/>
+      <x:c r="G46" s="42" t="str"/>
+      <x:c r="H46" s="42" t="str"/>
+      <x:c r="I46" s="42" t="str"/>
+      <x:c r="J46" s="42" t="str"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="18" t="str"/>
-      <x:c r="B47" s="19" t="str"/>
-      <x:c r="C47" s="19" t="str"/>
-      <x:c r="D47" s="18" t="str"/>
-      <x:c r="E47" s="18" t="str"/>
-      <x:c r="F47" s="20" t="str"/>
-      <x:c r="G47" s="18" t="str"/>
-      <x:c r="H47" s="18" t="str"/>
-      <x:c r="I47" s="18" t="str"/>
+      <x:c r="A47" s="42" t="str"/>
+      <x:c r="B47" s="43" t="str"/>
+      <x:c r="C47" s="43" t="str"/>
+      <x:c r="D47" s="42" t="str"/>
+      <x:c r="E47" s="42" t="str"/>
+      <x:c r="F47" s="44" t="str"/>
+      <x:c r="G47" s="42" t="str"/>
+      <x:c r="H47" s="42" t="str"/>
+      <x:c r="I47" s="42" t="str"/>
+      <x:c r="J47" s="42" t="str"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="18" t="str"/>
-      <x:c r="B48" s="19" t="str"/>
-      <x:c r="C48" s="19" t="str"/>
-      <x:c r="D48" s="18" t="str"/>
-      <x:c r="E48" s="18" t="str"/>
-      <x:c r="F48" s="20" t="str"/>
-      <x:c r="G48" s="18" t="str"/>
-      <x:c r="H48" s="18" t="str"/>
-      <x:c r="I48" s="18" t="str"/>
+      <x:c r="A48" s="42" t="str"/>
+      <x:c r="B48" s="43" t="str"/>
+      <x:c r="C48" s="43" t="str"/>
+      <x:c r="D48" s="42" t="str"/>
+      <x:c r="E48" s="42" t="str"/>
+      <x:c r="F48" s="44" t="str"/>
+      <x:c r="G48" s="42" t="str"/>
+      <x:c r="H48" s="42" t="str"/>
+      <x:c r="I48" s="42" t="str"/>
+      <x:c r="J48" s="42" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="18" t="str"/>
-      <x:c r="B49" s="19" t="str"/>
-      <x:c r="C49" s="19" t="str"/>
-      <x:c r="D49" s="18" t="str"/>
-      <x:c r="E49" s="18" t="str"/>
-      <x:c r="F49" s="20" t="str"/>
-      <x:c r="G49" s="18" t="str"/>
-      <x:c r="H49" s="18" t="str"/>
-      <x:c r="I49" s="18" t="str"/>
+      <x:c r="A49" s="42" t="str"/>
+      <x:c r="B49" s="43" t="str"/>
+      <x:c r="C49" s="43" t="str"/>
+      <x:c r="D49" s="42" t="str"/>
+      <x:c r="E49" s="42" t="str"/>
+      <x:c r="F49" s="44" t="str"/>
+      <x:c r="G49" s="42" t="str"/>
+      <x:c r="H49" s="42" t="str"/>
+      <x:c r="I49" s="42" t="str"/>
+      <x:c r="J49" s="42" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="18" t="str"/>
-      <x:c r="B50" s="19" t="str"/>
-      <x:c r="C50" s="19" t="str"/>
-      <x:c r="D50" s="18" t="str"/>
-      <x:c r="E50" s="18" t="str"/>
-      <x:c r="F50" s="20" t="str"/>
-      <x:c r="G50" s="18" t="str"/>
-      <x:c r="H50" s="18" t="str"/>
-      <x:c r="I50" s="18" t="str"/>
+      <x:c r="A50" s="42" t="str"/>
+      <x:c r="B50" s="43" t="str"/>
+      <x:c r="C50" s="43" t="str"/>
+      <x:c r="D50" s="42" t="str"/>
+      <x:c r="E50" s="42" t="str"/>
+      <x:c r="F50" s="44" t="str"/>
+      <x:c r="G50" s="42" t="str"/>
+      <x:c r="H50" s="42" t="str"/>
+      <x:c r="I50" s="42" t="str"/>
+      <x:c r="J50" s="42" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="18" t="str"/>
-      <x:c r="B51" s="19" t="str"/>
-      <x:c r="C51" s="19" t="str"/>
-      <x:c r="D51" s="18" t="str"/>
-      <x:c r="E51" s="18" t="str"/>
-      <x:c r="F51" s="20" t="str"/>
-      <x:c r="G51" s="18" t="str"/>
-      <x:c r="H51" s="18" t="str"/>
-      <x:c r="I51" s="18" t="str"/>
+      <x:c r="A51" s="42" t="str"/>
+      <x:c r="B51" s="43" t="str"/>
+      <x:c r="C51" s="43" t="str"/>
+      <x:c r="D51" s="42" t="str"/>
+      <x:c r="E51" s="42" t="str"/>
+      <x:c r="F51" s="44" t="str"/>
+      <x:c r="G51" s="42" t="str"/>
+      <x:c r="H51" s="42" t="str"/>
+      <x:c r="I51" s="42" t="str"/>
+      <x:c r="J51" s="42" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1177,11 +1285,203 @@
         <x:v>地図側 F023 ＋ Excel側 F023 → F023の既存ポイントへ情報を反映します．</x:v>
       </x:c>
     </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="50" t="str">
+        <x:v>おすすめの作業フロー</x:v>
+      </x:c>
+      <x:c r="B31" s="50" t="str"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="11" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B32" s="11" t="str">
+        <x:v>WebアプリでGPXや地図クリックから位置ポイントを作成し，地点番号を付けます．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="11" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B33" s="11" t="str">
+        <x:v>Webアプリの「現在のポイントから入力用Excelを作成」を押します．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="11" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B34" s="11" t="str">
+        <x:v>地点番号と緯度・経度が入ったExcelがダウンロードされます．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="11" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B35" s="11" t="str">
+        <x:v>Excelで走向，傾斜，測定日，岩種・地層名，面・構造，色区分，補足情報を入力します．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="11" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B36" s="11" t="str">
+        <x:v>ExcelをWebアプリへ読み込むと，地点番号が一致する既存ポイントへ反映されます．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="11" t="str">
+        <x:v>色区分</x:v>
+      </x:c>
+      <x:c r="B37" s="11" t="str">
+        <x:v>「色定義」シートで色区分名とHEX色を自由に定義できます．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="11" t="str">
+        <x:v>色の例</x:v>
+      </x:c>
+      <x:c r="B38" s="11" t="str">
+        <x:v>黒 #111111，赤 #d62728，青 #1f77b4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="11" t="str">
+        <x:v>地点番号</x:v>
+      </x:c>
+      <x:c r="B39" s="11" t="str">
+        <x:v>既存ポイントとの対応キーなので，意図なく変更しないことを推奨します．</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="11" t="str">
+        <x:v>座標</x:v>
+      </x:c>
+      <x:c r="B40" s="11" t="str">
+        <x:v>既存ポイントへ反映するだけなら，Excel側の緯度・経度は空欄でも構いません．</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:B1"/>
     <x:mergeCell ref="A23:B23"/>
+    <x:mergeCell ref="A31:B31"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="46" t="str">
+        <x:v>色区分</x:v>
+      </x:c>
+      <x:c r="B1" s="46" t="str">
+        <x:v>色(HEX)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>標準</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>#111111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>層理面</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>#111111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>亀裂</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>#d62728</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>層面すべり面</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>#1f77b4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11"/>
+      <x:c r="B6" s="11"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11"/>
+      <x:c r="B7" s="11"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11"/>
+      <x:c r="B8" s="11"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11"/>
+      <x:c r="B9" s="11"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11"/>
+      <x:c r="B10" s="11"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11"/>
+      <x:c r="B11" s="11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11"/>
+      <x:c r="B12" s="11"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11"/>
+      <x:c r="B13" s="11"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11"/>
+      <x:c r="B14" s="11"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11"/>
+      <x:c r="B15" s="11"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11"/>
+      <x:c r="B16" s="11"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11"/>
+      <x:c r="B17" s="11"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11"/>
+      <x:c r="B18" s="11"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="11"/>
+      <x:c r="B19" s="11"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="11"/>
+      <x:c r="B20" s="11"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/strike_dip_import_template.xlsx
+++ b/strike_dip_import_template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力テンプレート" sheetId="1" r:id="R6450cb6715954a53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記入例・説明" sheetId="2" r:id="Rb63361bee9914c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色定義" sheetId="3" r:id="Rb42e40b4a1c14125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="入力テンプレート" sheetId="1" r:id="Rf91fcfc3c5b84660"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記入例・説明" sheetId="2" r:id="Rb1c0ca616dc34bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="色定義" sheetId="3" r:id="R281596bb2b964fbb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +19,7 @@
     <x:numFmt numFmtId="200" formatCode="0.000000"/>
     <x:numFmt numFmtId="201" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="3">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,8 +35,23 @@
       <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="BIZ UDPGothic"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="BIZ UDPGothic"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="BIZ UDPGothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -78,6 +93,16 @@
         <x:fgColor rgb="FFD9E6F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF315B7D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E6F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -86,7 +111,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="51">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -202,6 +227,44 @@
       <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -419,636 +482,636 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="37" t="str">
+      <x:c r="A1" s="61" t="str">
         <x:v>地点番号</x:v>
       </x:c>
-      <x:c r="B1" s="37" t="str">
+      <x:c r="B1" s="61" t="str">
         <x:v>緯度</x:v>
       </x:c>
-      <x:c r="C1" s="37" t="str">
+      <x:c r="C1" s="61" t="str">
         <x:v>経度</x:v>
       </x:c>
-      <x:c r="D1" s="37" t="str">
+      <x:c r="D1" s="61" t="str">
         <x:v>走向</x:v>
       </x:c>
-      <x:c r="E1" s="37" t="str">
+      <x:c r="E1" s="61" t="str">
         <x:v>傾斜</x:v>
       </x:c>
-      <x:c r="F1" s="37" t="str">
+      <x:c r="F1" s="61" t="str">
         <x:v>測定日</x:v>
       </x:c>
-      <x:c r="G1" s="37" t="str">
+      <x:c r="G1" s="61" t="str">
         <x:v>岩種・地層名</x:v>
       </x:c>
-      <x:c r="H1" s="37" t="str">
+      <x:c r="H1" s="61" t="str">
         <x:v>面・構造</x:v>
       </x:c>
-      <x:c r="I1" s="37" t="str">
+      <x:c r="I1" s="61" t="str">
         <x:v>色区分</x:v>
       </x:c>
-      <x:c r="J1" s="37" t="str">
+      <x:c r="J1" s="61" t="str">
         <x:v>補足情報</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="42" t="str"/>
-      <x:c r="B2" s="43" t="str"/>
-      <x:c r="C2" s="43" t="str"/>
-      <x:c r="D2" s="42" t="str"/>
-      <x:c r="E2" s="42" t="str"/>
-      <x:c r="F2" s="44" t="str"/>
-      <x:c r="G2" s="42" t="str"/>
-      <x:c r="H2" s="42" t="str"/>
-      <x:c r="I2" s="42" t="str"/>
-      <x:c r="J2" s="42" t="str"/>
+      <x:c r="A2" s="53" t="str"/>
+      <x:c r="B2" s="54" t="str"/>
+      <x:c r="C2" s="54" t="str"/>
+      <x:c r="D2" s="53" t="str"/>
+      <x:c r="E2" s="53" t="str"/>
+      <x:c r="F2" s="55" t="str"/>
+      <x:c r="G2" s="53" t="str"/>
+      <x:c r="H2" s="53" t="str"/>
+      <x:c r="I2" s="53" t="str"/>
+      <x:c r="J2" s="53" t="str"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="42" t="str"/>
-      <x:c r="B3" s="43" t="str"/>
-      <x:c r="C3" s="43" t="str"/>
-      <x:c r="D3" s="42" t="str"/>
-      <x:c r="E3" s="42" t="str"/>
-      <x:c r="F3" s="44" t="str"/>
-      <x:c r="G3" s="42" t="str"/>
-      <x:c r="H3" s="42" t="str"/>
-      <x:c r="I3" s="42" t="str"/>
-      <x:c r="J3" s="42" t="str"/>
+      <x:c r="A3" s="53" t="str"/>
+      <x:c r="B3" s="54" t="str"/>
+      <x:c r="C3" s="54" t="str"/>
+      <x:c r="D3" s="53" t="str"/>
+      <x:c r="E3" s="53" t="str"/>
+      <x:c r="F3" s="55" t="str"/>
+      <x:c r="G3" s="53" t="str"/>
+      <x:c r="H3" s="53" t="str"/>
+      <x:c r="I3" s="53" t="str"/>
+      <x:c r="J3" s="53" t="str"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="42" t="str"/>
-      <x:c r="B4" s="43" t="str"/>
-      <x:c r="C4" s="43" t="str"/>
-      <x:c r="D4" s="42" t="str"/>
-      <x:c r="E4" s="42" t="str"/>
-      <x:c r="F4" s="44" t="str"/>
-      <x:c r="G4" s="42" t="str"/>
-      <x:c r="H4" s="42" t="str"/>
-      <x:c r="I4" s="42" t="str"/>
-      <x:c r="J4" s="42" t="str"/>
+      <x:c r="A4" s="53" t="str"/>
+      <x:c r="B4" s="54" t="str"/>
+      <x:c r="C4" s="54" t="str"/>
+      <x:c r="D4" s="53" t="str"/>
+      <x:c r="E4" s="53" t="str"/>
+      <x:c r="F4" s="55" t="str"/>
+      <x:c r="G4" s="53" t="str"/>
+      <x:c r="H4" s="53" t="str"/>
+      <x:c r="I4" s="53" t="str"/>
+      <x:c r="J4" s="53" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="42" t="str"/>
-      <x:c r="B5" s="43" t="str"/>
-      <x:c r="C5" s="43" t="str"/>
-      <x:c r="D5" s="42" t="str"/>
-      <x:c r="E5" s="42" t="str"/>
-      <x:c r="F5" s="44" t="str"/>
-      <x:c r="G5" s="42" t="str"/>
-      <x:c r="H5" s="42" t="str"/>
-      <x:c r="I5" s="42" t="str"/>
-      <x:c r="J5" s="42" t="str"/>
+      <x:c r="A5" s="53" t="str"/>
+      <x:c r="B5" s="54" t="str"/>
+      <x:c r="C5" s="54" t="str"/>
+      <x:c r="D5" s="53" t="str"/>
+      <x:c r="E5" s="53" t="str"/>
+      <x:c r="F5" s="55" t="str"/>
+      <x:c r="G5" s="53" t="str"/>
+      <x:c r="H5" s="53" t="str"/>
+      <x:c r="I5" s="53" t="str"/>
+      <x:c r="J5" s="53" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="42" t="str"/>
-      <x:c r="B6" s="43" t="str"/>
-      <x:c r="C6" s="43" t="str"/>
-      <x:c r="D6" s="42" t="str"/>
-      <x:c r="E6" s="42" t="str"/>
-      <x:c r="F6" s="44" t="str"/>
-      <x:c r="G6" s="42" t="str"/>
-      <x:c r="H6" s="42" t="str"/>
-      <x:c r="I6" s="42" t="str"/>
-      <x:c r="J6" s="42" t="str"/>
+      <x:c r="A6" s="53" t="str"/>
+      <x:c r="B6" s="54" t="str"/>
+      <x:c r="C6" s="54" t="str"/>
+      <x:c r="D6" s="53" t="str"/>
+      <x:c r="E6" s="53" t="str"/>
+      <x:c r="F6" s="55" t="str"/>
+      <x:c r="G6" s="53" t="str"/>
+      <x:c r="H6" s="53" t="str"/>
+      <x:c r="I6" s="53" t="str"/>
+      <x:c r="J6" s="53" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="42" t="str"/>
-      <x:c r="B7" s="43" t="str"/>
-      <x:c r="C7" s="43" t="str"/>
-      <x:c r="D7" s="42" t="str"/>
-      <x:c r="E7" s="42" t="str"/>
-      <x:c r="F7" s="44" t="str"/>
-      <x:c r="G7" s="42" t="str"/>
-      <x:c r="H7" s="42" t="str"/>
-      <x:c r="I7" s="42" t="str"/>
-      <x:c r="J7" s="42" t="str"/>
+      <x:c r="A7" s="53" t="str"/>
+      <x:c r="B7" s="54" t="str"/>
+      <x:c r="C7" s="54" t="str"/>
+      <x:c r="D7" s="53" t="str"/>
+      <x:c r="E7" s="53" t="str"/>
+      <x:c r="F7" s="55" t="str"/>
+      <x:c r="G7" s="53" t="str"/>
+      <x:c r="H7" s="53" t="str"/>
+      <x:c r="I7" s="53" t="str"/>
+      <x:c r="J7" s="53" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="42" t="str"/>
-      <x:c r="B8" s="43" t="str"/>
-      <x:c r="C8" s="43" t="str"/>
-      <x:c r="D8" s="42" t="str"/>
-      <x:c r="E8" s="42" t="str"/>
-      <x:c r="F8" s="44" t="str"/>
-      <x:c r="G8" s="42" t="str"/>
-      <x:c r="H8" s="42" t="str"/>
-      <x:c r="I8" s="42" t="str"/>
-      <x:c r="J8" s="42" t="str"/>
+      <x:c r="A8" s="53" t="str"/>
+      <x:c r="B8" s="54" t="str"/>
+      <x:c r="C8" s="54" t="str"/>
+      <x:c r="D8" s="53" t="str"/>
+      <x:c r="E8" s="53" t="str"/>
+      <x:c r="F8" s="55" t="str"/>
+      <x:c r="G8" s="53" t="str"/>
+      <x:c r="H8" s="53" t="str"/>
+      <x:c r="I8" s="53" t="str"/>
+      <x:c r="J8" s="53" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="42" t="str"/>
-      <x:c r="B9" s="43" t="str"/>
-      <x:c r="C9" s="43" t="str"/>
-      <x:c r="D9" s="42" t="str"/>
-      <x:c r="E9" s="42" t="str"/>
-      <x:c r="F9" s="44" t="str"/>
-      <x:c r="G9" s="42" t="str"/>
-      <x:c r="H9" s="42" t="str"/>
-      <x:c r="I9" s="42" t="str"/>
-      <x:c r="J9" s="42" t="str"/>
+      <x:c r="A9" s="53" t="str"/>
+      <x:c r="B9" s="54" t="str"/>
+      <x:c r="C9" s="54" t="str"/>
+      <x:c r="D9" s="53" t="str"/>
+      <x:c r="E9" s="53" t="str"/>
+      <x:c r="F9" s="55" t="str"/>
+      <x:c r="G9" s="53" t="str"/>
+      <x:c r="H9" s="53" t="str"/>
+      <x:c r="I9" s="53" t="str"/>
+      <x:c r="J9" s="53" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="42" t="str"/>
-      <x:c r="B10" s="43" t="str"/>
-      <x:c r="C10" s="43" t="str"/>
-      <x:c r="D10" s="42" t="str"/>
-      <x:c r="E10" s="42" t="str"/>
-      <x:c r="F10" s="44" t="str"/>
-      <x:c r="G10" s="42" t="str"/>
-      <x:c r="H10" s="42" t="str"/>
-      <x:c r="I10" s="42" t="str"/>
-      <x:c r="J10" s="42" t="str"/>
+      <x:c r="A10" s="53" t="str"/>
+      <x:c r="B10" s="54" t="str"/>
+      <x:c r="C10" s="54" t="str"/>
+      <x:c r="D10" s="53" t="str"/>
+      <x:c r="E10" s="53" t="str"/>
+      <x:c r="F10" s="55" t="str"/>
+      <x:c r="G10" s="53" t="str"/>
+      <x:c r="H10" s="53" t="str"/>
+      <x:c r="I10" s="53" t="str"/>
+      <x:c r="J10" s="53" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="42" t="str"/>
-      <x:c r="B11" s="43" t="str"/>
-      <x:c r="C11" s="43" t="str"/>
-      <x:c r="D11" s="42" t="str"/>
-      <x:c r="E11" s="42" t="str"/>
-      <x:c r="F11" s="44" t="str"/>
-      <x:c r="G11" s="42" t="str"/>
-      <x:c r="H11" s="42" t="str"/>
-      <x:c r="I11" s="42" t="str"/>
-      <x:c r="J11" s="42" t="str"/>
+      <x:c r="A11" s="53" t="str"/>
+      <x:c r="B11" s="54" t="str"/>
+      <x:c r="C11" s="54" t="str"/>
+      <x:c r="D11" s="53" t="str"/>
+      <x:c r="E11" s="53" t="str"/>
+      <x:c r="F11" s="55" t="str"/>
+      <x:c r="G11" s="53" t="str"/>
+      <x:c r="H11" s="53" t="str"/>
+      <x:c r="I11" s="53" t="str"/>
+      <x:c r="J11" s="53" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="42" t="str"/>
-      <x:c r="B12" s="43" t="str"/>
-      <x:c r="C12" s="43" t="str"/>
-      <x:c r="D12" s="42" t="str"/>
-      <x:c r="E12" s="42" t="str"/>
-      <x:c r="F12" s="44" t="str"/>
-      <x:c r="G12" s="42" t="str"/>
-      <x:c r="H12" s="42" t="str"/>
-      <x:c r="I12" s="42" t="str"/>
-      <x:c r="J12" s="42" t="str"/>
+      <x:c r="A12" s="53" t="str"/>
+      <x:c r="B12" s="54" t="str"/>
+      <x:c r="C12" s="54" t="str"/>
+      <x:c r="D12" s="53" t="str"/>
+      <x:c r="E12" s="53" t="str"/>
+      <x:c r="F12" s="55" t="str"/>
+      <x:c r="G12" s="53" t="str"/>
+      <x:c r="H12" s="53" t="str"/>
+      <x:c r="I12" s="53" t="str"/>
+      <x:c r="J12" s="53" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="42" t="str"/>
-      <x:c r="B13" s="43" t="str"/>
-      <x:c r="C13" s="43" t="str"/>
-      <x:c r="D13" s="42" t="str"/>
-      <x:c r="E13" s="42" t="str"/>
-      <x:c r="F13" s="44" t="str"/>
-      <x:c r="G13" s="42" t="str"/>
-      <x:c r="H13" s="42" t="str"/>
-      <x:c r="I13" s="42" t="str"/>
-      <x:c r="J13" s="42" t="str"/>
+      <x:c r="A13" s="53" t="str"/>
+      <x:c r="B13" s="54" t="str"/>
+      <x:c r="C13" s="54" t="str"/>
+      <x:c r="D13" s="53" t="str"/>
+      <x:c r="E13" s="53" t="str"/>
+      <x:c r="F13" s="55" t="str"/>
+      <x:c r="G13" s="53" t="str"/>
+      <x:c r="H13" s="53" t="str"/>
+      <x:c r="I13" s="53" t="str"/>
+      <x:c r="J13" s="53" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="42" t="str"/>
-      <x:c r="B14" s="43" t="str"/>
-      <x:c r="C14" s="43" t="str"/>
-      <x:c r="D14" s="42" t="str"/>
-      <x:c r="E14" s="42" t="str"/>
-      <x:c r="F14" s="44" t="str"/>
-      <x:c r="G14" s="42" t="str"/>
-      <x:c r="H14" s="42" t="str"/>
-      <x:c r="I14" s="42" t="str"/>
-      <x:c r="J14" s="42" t="str"/>
+      <x:c r="A14" s="53" t="str"/>
+      <x:c r="B14" s="54" t="str"/>
+      <x:c r="C14" s="54" t="str"/>
+      <x:c r="D14" s="53" t="str"/>
+      <x:c r="E14" s="53" t="str"/>
+      <x:c r="F14" s="55" t="str"/>
+      <x:c r="G14" s="53" t="str"/>
+      <x:c r="H14" s="53" t="str"/>
+      <x:c r="I14" s="53" t="str"/>
+      <x:c r="J14" s="53" t="str"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="42" t="str"/>
-      <x:c r="B15" s="43" t="str"/>
-      <x:c r="C15" s="43" t="str"/>
-      <x:c r="D15" s="42" t="str"/>
-      <x:c r="E15" s="42" t="str"/>
-      <x:c r="F15" s="44" t="str"/>
-      <x:c r="G15" s="42" t="str"/>
-      <x:c r="H15" s="42" t="str"/>
-      <x:c r="I15" s="42" t="str"/>
-      <x:c r="J15" s="42" t="str"/>
+      <x:c r="A15" s="53" t="str"/>
+      <x:c r="B15" s="54" t="str"/>
+      <x:c r="C15" s="54" t="str"/>
+      <x:c r="D15" s="53" t="str"/>
+      <x:c r="E15" s="53" t="str"/>
+      <x:c r="F15" s="55" t="str"/>
+      <x:c r="G15" s="53" t="str"/>
+      <x:c r="H15" s="53" t="str"/>
+      <x:c r="I15" s="53" t="str"/>
+      <x:c r="J15" s="53" t="str"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="42" t="str"/>
-      <x:c r="B16" s="43" t="str"/>
-      <x:c r="C16" s="43" t="str"/>
-      <x:c r="D16" s="42" t="str"/>
-      <x:c r="E16" s="42" t="str"/>
-      <x:c r="F16" s="44" t="str"/>
-      <x:c r="G16" s="42" t="str"/>
-      <x:c r="H16" s="42" t="str"/>
-      <x:c r="I16" s="42" t="str"/>
-      <x:c r="J16" s="42" t="str"/>
+      <x:c r="A16" s="53" t="str"/>
+      <x:c r="B16" s="54" t="str"/>
+      <x:c r="C16" s="54" t="str"/>
+      <x:c r="D16" s="53" t="str"/>
+      <x:c r="E16" s="53" t="str"/>
+      <x:c r="F16" s="55" t="str"/>
+      <x:c r="G16" s="53" t="str"/>
+      <x:c r="H16" s="53" t="str"/>
+      <x:c r="I16" s="53" t="str"/>
+      <x:c r="J16" s="53" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="42" t="str"/>
-      <x:c r="B17" s="43" t="str"/>
-      <x:c r="C17" s="43" t="str"/>
-      <x:c r="D17" s="42" t="str"/>
-      <x:c r="E17" s="42" t="str"/>
-      <x:c r="F17" s="44" t="str"/>
-      <x:c r="G17" s="42" t="str"/>
-      <x:c r="H17" s="42" t="str"/>
-      <x:c r="I17" s="42" t="str"/>
-      <x:c r="J17" s="42" t="str"/>
+      <x:c r="A17" s="53" t="str"/>
+      <x:c r="B17" s="54" t="str"/>
+      <x:c r="C17" s="54" t="str"/>
+      <x:c r="D17" s="53" t="str"/>
+      <x:c r="E17" s="53" t="str"/>
+      <x:c r="F17" s="55" t="str"/>
+      <x:c r="G17" s="53" t="str"/>
+      <x:c r="H17" s="53" t="str"/>
+      <x:c r="I17" s="53" t="str"/>
+      <x:c r="J17" s="53" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="42" t="str"/>
-      <x:c r="B18" s="43" t="str"/>
-      <x:c r="C18" s="43" t="str"/>
-      <x:c r="D18" s="42" t="str"/>
-      <x:c r="E18" s="42" t="str"/>
-      <x:c r="F18" s="44" t="str"/>
-      <x:c r="G18" s="42" t="str"/>
-      <x:c r="H18" s="42" t="str"/>
-      <x:c r="I18" s="42" t="str"/>
-      <x:c r="J18" s="42" t="str"/>
+      <x:c r="A18" s="53" t="str"/>
+      <x:c r="B18" s="54" t="str"/>
+      <x:c r="C18" s="54" t="str"/>
+      <x:c r="D18" s="53" t="str"/>
+      <x:c r="E18" s="53" t="str"/>
+      <x:c r="F18" s="55" t="str"/>
+      <x:c r="G18" s="53" t="str"/>
+      <x:c r="H18" s="53" t="str"/>
+      <x:c r="I18" s="53" t="str"/>
+      <x:c r="J18" s="53" t="str"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="42" t="str"/>
-      <x:c r="B19" s="43" t="str"/>
-      <x:c r="C19" s="43" t="str"/>
-      <x:c r="D19" s="42" t="str"/>
-      <x:c r="E19" s="42" t="str"/>
-      <x:c r="F19" s="44" t="str"/>
-      <x:c r="G19" s="42" t="str"/>
-      <x:c r="H19" s="42" t="str"/>
-      <x:c r="I19" s="42" t="str"/>
-      <x:c r="J19" s="42" t="str"/>
+      <x:c r="A19" s="53" t="str"/>
+      <x:c r="B19" s="54" t="str"/>
+      <x:c r="C19" s="54" t="str"/>
+      <x:c r="D19" s="53" t="str"/>
+      <x:c r="E19" s="53" t="str"/>
+      <x:c r="F19" s="55" t="str"/>
+      <x:c r="G19" s="53" t="str"/>
+      <x:c r="H19" s="53" t="str"/>
+      <x:c r="I19" s="53" t="str"/>
+      <x:c r="J19" s="53" t="str"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="42" t="str"/>
-      <x:c r="B20" s="43" t="str"/>
-      <x:c r="C20" s="43" t="str"/>
-      <x:c r="D20" s="42" t="str"/>
-      <x:c r="E20" s="42" t="str"/>
-      <x:c r="F20" s="44" t="str"/>
-      <x:c r="G20" s="42" t="str"/>
-      <x:c r="H20" s="42" t="str"/>
-      <x:c r="I20" s="42" t="str"/>
-      <x:c r="J20" s="42" t="str"/>
+      <x:c r="A20" s="53" t="str"/>
+      <x:c r="B20" s="54" t="str"/>
+      <x:c r="C20" s="54" t="str"/>
+      <x:c r="D20" s="53" t="str"/>
+      <x:c r="E20" s="53" t="str"/>
+      <x:c r="F20" s="55" t="str"/>
+      <x:c r="G20" s="53" t="str"/>
+      <x:c r="H20" s="53" t="str"/>
+      <x:c r="I20" s="53" t="str"/>
+      <x:c r="J20" s="53" t="str"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="42" t="str"/>
-      <x:c r="B21" s="43" t="str"/>
-      <x:c r="C21" s="43" t="str"/>
-      <x:c r="D21" s="42" t="str"/>
-      <x:c r="E21" s="42" t="str"/>
-      <x:c r="F21" s="44" t="str"/>
-      <x:c r="G21" s="42" t="str"/>
-      <x:c r="H21" s="42" t="str"/>
-      <x:c r="I21" s="42" t="str"/>
-      <x:c r="J21" s="42" t="str"/>
+      <x:c r="A21" s="53" t="str"/>
+      <x:c r="B21" s="54" t="str"/>
+      <x:c r="C21" s="54" t="str"/>
+      <x:c r="D21" s="53" t="str"/>
+      <x:c r="E21" s="53" t="str"/>
+      <x:c r="F21" s="55" t="str"/>
+      <x:c r="G21" s="53" t="str"/>
+      <x:c r="H21" s="53" t="str"/>
+      <x:c r="I21" s="53" t="str"/>
+      <x:c r="J21" s="53" t="str"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="42" t="str"/>
-      <x:c r="B22" s="43" t="str"/>
-      <x:c r="C22" s="43" t="str"/>
-      <x:c r="D22" s="42" t="str"/>
-      <x:c r="E22" s="42" t="str"/>
-      <x:c r="F22" s="44" t="str"/>
-      <x:c r="G22" s="42" t="str"/>
-      <x:c r="H22" s="42" t="str"/>
-      <x:c r="I22" s="42" t="str"/>
-      <x:c r="J22" s="42" t="str"/>
+      <x:c r="A22" s="53" t="str"/>
+      <x:c r="B22" s="54" t="str"/>
+      <x:c r="C22" s="54" t="str"/>
+      <x:c r="D22" s="53" t="str"/>
+      <x:c r="E22" s="53" t="str"/>
+      <x:c r="F22" s="55" t="str"/>
+      <x:c r="G22" s="53" t="str"/>
+      <x:c r="H22" s="53" t="str"/>
+      <x:c r="I22" s="53" t="str"/>
+      <x:c r="J22" s="53" t="str"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="42" t="str"/>
-      <x:c r="B23" s="43" t="str"/>
-      <x:c r="C23" s="43" t="str"/>
-      <x:c r="D23" s="42" t="str"/>
-      <x:c r="E23" s="42" t="str"/>
-      <x:c r="F23" s="44" t="str"/>
-      <x:c r="G23" s="42" t="str"/>
-      <x:c r="H23" s="42" t="str"/>
-      <x:c r="I23" s="42" t="str"/>
-      <x:c r="J23" s="42" t="str"/>
+      <x:c r="A23" s="53" t="str"/>
+      <x:c r="B23" s="54" t="str"/>
+      <x:c r="C23" s="54" t="str"/>
+      <x:c r="D23" s="53" t="str"/>
+      <x:c r="E23" s="53" t="str"/>
+      <x:c r="F23" s="55" t="str"/>
+      <x:c r="G23" s="53" t="str"/>
+      <x:c r="H23" s="53" t="str"/>
+      <x:c r="I23" s="53" t="str"/>
+      <x:c r="J23" s="53" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="42" t="str"/>
-      <x:c r="B24" s="43" t="str"/>
-      <x:c r="C24" s="43" t="str"/>
-      <x:c r="D24" s="42" t="str"/>
-      <x:c r="E24" s="42" t="str"/>
-      <x:c r="F24" s="44" t="str"/>
-      <x:c r="G24" s="42" t="str"/>
-      <x:c r="H24" s="42" t="str"/>
-      <x:c r="I24" s="42" t="str"/>
-      <x:c r="J24" s="42" t="str"/>
+      <x:c r="A24" s="53" t="str"/>
+      <x:c r="B24" s="54" t="str"/>
+      <x:c r="C24" s="54" t="str"/>
+      <x:c r="D24" s="53" t="str"/>
+      <x:c r="E24" s="53" t="str"/>
+      <x:c r="F24" s="55" t="str"/>
+      <x:c r="G24" s="53" t="str"/>
+      <x:c r="H24" s="53" t="str"/>
+      <x:c r="I24" s="53" t="str"/>
+      <x:c r="J24" s="53" t="str"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="42" t="str"/>
-      <x:c r="B25" s="43" t="str"/>
-      <x:c r="C25" s="43" t="str"/>
-      <x:c r="D25" s="42" t="str"/>
-      <x:c r="E25" s="42" t="str"/>
-      <x:c r="F25" s="44" t="str"/>
-      <x:c r="G25" s="42" t="str"/>
-      <x:c r="H25" s="42" t="str"/>
-      <x:c r="I25" s="42" t="str"/>
-      <x:c r="J25" s="42" t="str"/>
+      <x:c r="A25" s="53" t="str"/>
+      <x:c r="B25" s="54" t="str"/>
+      <x:c r="C25" s="54" t="str"/>
+      <x:c r="D25" s="53" t="str"/>
+      <x:c r="E25" s="53" t="str"/>
+      <x:c r="F25" s="55" t="str"/>
+      <x:c r="G25" s="53" t="str"/>
+      <x:c r="H25" s="53" t="str"/>
+      <x:c r="I25" s="53" t="str"/>
+      <x:c r="J25" s="53" t="str"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="42" t="str"/>
-      <x:c r="B26" s="43" t="str"/>
-      <x:c r="C26" s="43" t="str"/>
-      <x:c r="D26" s="42" t="str"/>
-      <x:c r="E26" s="42" t="str"/>
-      <x:c r="F26" s="44" t="str"/>
-      <x:c r="G26" s="42" t="str"/>
-      <x:c r="H26" s="42" t="str"/>
-      <x:c r="I26" s="42" t="str"/>
-      <x:c r="J26" s="42" t="str"/>
+      <x:c r="A26" s="53" t="str"/>
+      <x:c r="B26" s="54" t="str"/>
+      <x:c r="C26" s="54" t="str"/>
+      <x:c r="D26" s="53" t="str"/>
+      <x:c r="E26" s="53" t="str"/>
+      <x:c r="F26" s="55" t="str"/>
+      <x:c r="G26" s="53" t="str"/>
+      <x:c r="H26" s="53" t="str"/>
+      <x:c r="I26" s="53" t="str"/>
+      <x:c r="J26" s="53" t="str"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="42" t="str"/>
-      <x:c r="B27" s="43" t="str"/>
-      <x:c r="C27" s="43" t="str"/>
-      <x:c r="D27" s="42" t="str"/>
-      <x:c r="E27" s="42" t="str"/>
-      <x:c r="F27" s="44" t="str"/>
-      <x:c r="G27" s="42" t="str"/>
-      <x:c r="H27" s="42" t="str"/>
-      <x:c r="I27" s="42" t="str"/>
-      <x:c r="J27" s="42" t="str"/>
+      <x:c r="A27" s="53" t="str"/>
+      <x:c r="B27" s="54" t="str"/>
+      <x:c r="C27" s="54" t="str"/>
+      <x:c r="D27" s="53" t="str"/>
+      <x:c r="E27" s="53" t="str"/>
+      <x:c r="F27" s="55" t="str"/>
+      <x:c r="G27" s="53" t="str"/>
+      <x:c r="H27" s="53" t="str"/>
+      <x:c r="I27" s="53" t="str"/>
+      <x:c r="J27" s="53" t="str"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="42" t="str"/>
-      <x:c r="B28" s="43" t="str"/>
-      <x:c r="C28" s="43" t="str"/>
-      <x:c r="D28" s="42" t="str"/>
-      <x:c r="E28" s="42" t="str"/>
-      <x:c r="F28" s="44" t="str"/>
-      <x:c r="G28" s="42" t="str"/>
-      <x:c r="H28" s="42" t="str"/>
-      <x:c r="I28" s="42" t="str"/>
-      <x:c r="J28" s="42" t="str"/>
+      <x:c r="A28" s="53" t="str"/>
+      <x:c r="B28" s="54" t="str"/>
+      <x:c r="C28" s="54" t="str"/>
+      <x:c r="D28" s="53" t="str"/>
+      <x:c r="E28" s="53" t="str"/>
+      <x:c r="F28" s="55" t="str"/>
+      <x:c r="G28" s="53" t="str"/>
+      <x:c r="H28" s="53" t="str"/>
+      <x:c r="I28" s="53" t="str"/>
+      <x:c r="J28" s="53" t="str"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="42" t="str"/>
-      <x:c r="B29" s="43" t="str"/>
-      <x:c r="C29" s="43" t="str"/>
-      <x:c r="D29" s="42" t="str"/>
-      <x:c r="E29" s="42" t="str"/>
-      <x:c r="F29" s="44" t="str"/>
-      <x:c r="G29" s="42" t="str"/>
-      <x:c r="H29" s="42" t="str"/>
-      <x:c r="I29" s="42" t="str"/>
-      <x:c r="J29" s="42" t="str"/>
+      <x:c r="A29" s="53" t="str"/>
+      <x:c r="B29" s="54" t="str"/>
+      <x:c r="C29" s="54" t="str"/>
+      <x:c r="D29" s="53" t="str"/>
+      <x:c r="E29" s="53" t="str"/>
+      <x:c r="F29" s="55" t="str"/>
+      <x:c r="G29" s="53" t="str"/>
+      <x:c r="H29" s="53" t="str"/>
+      <x:c r="I29" s="53" t="str"/>
+      <x:c r="J29" s="53" t="str"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="42" t="str"/>
-      <x:c r="B30" s="43" t="str"/>
-      <x:c r="C30" s="43" t="str"/>
-      <x:c r="D30" s="42" t="str"/>
-      <x:c r="E30" s="42" t="str"/>
-      <x:c r="F30" s="44" t="str"/>
-      <x:c r="G30" s="42" t="str"/>
-      <x:c r="H30" s="42" t="str"/>
-      <x:c r="I30" s="42" t="str"/>
-      <x:c r="J30" s="42" t="str"/>
+      <x:c r="A30" s="53" t="str"/>
+      <x:c r="B30" s="54" t="str"/>
+      <x:c r="C30" s="54" t="str"/>
+      <x:c r="D30" s="53" t="str"/>
+      <x:c r="E30" s="53" t="str"/>
+      <x:c r="F30" s="55" t="str"/>
+      <x:c r="G30" s="53" t="str"/>
+      <x:c r="H30" s="53" t="str"/>
+      <x:c r="I30" s="53" t="str"/>
+      <x:c r="J30" s="53" t="str"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="42" t="str"/>
-      <x:c r="B31" s="43" t="str"/>
-      <x:c r="C31" s="43" t="str"/>
-      <x:c r="D31" s="42" t="str"/>
-      <x:c r="E31" s="42" t="str"/>
-      <x:c r="F31" s="44" t="str"/>
-      <x:c r="G31" s="42" t="str"/>
-      <x:c r="H31" s="42" t="str"/>
-      <x:c r="I31" s="42" t="str"/>
-      <x:c r="J31" s="42" t="str"/>
+      <x:c r="A31" s="53" t="str"/>
+      <x:c r="B31" s="54" t="str"/>
+      <x:c r="C31" s="54" t="str"/>
+      <x:c r="D31" s="53" t="str"/>
+      <x:c r="E31" s="53" t="str"/>
+      <x:c r="F31" s="55" t="str"/>
+      <x:c r="G31" s="53" t="str"/>
+      <x:c r="H31" s="53" t="str"/>
+      <x:c r="I31" s="53" t="str"/>
+      <x:c r="J31" s="53" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="42" t="str"/>
-      <x:c r="B32" s="43" t="str"/>
-      <x:c r="C32" s="43" t="str"/>
-      <x:c r="D32" s="42" t="str"/>
-      <x:c r="E32" s="42" t="str"/>
-      <x:c r="F32" s="44" t="str"/>
-      <x:c r="G32" s="42" t="str"/>
-      <x:c r="H32" s="42" t="str"/>
-      <x:c r="I32" s="42" t="str"/>
-      <x:c r="J32" s="42" t="str"/>
+      <x:c r="A32" s="53" t="str"/>
+      <x:c r="B32" s="54" t="str"/>
+      <x:c r="C32" s="54" t="str"/>
+      <x:c r="D32" s="53" t="str"/>
+      <x:c r="E32" s="53" t="str"/>
+      <x:c r="F32" s="55" t="str"/>
+      <x:c r="G32" s="53" t="str"/>
+      <x:c r="H32" s="53" t="str"/>
+      <x:c r="I32" s="53" t="str"/>
+      <x:c r="J32" s="53" t="str"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="42" t="str"/>
-      <x:c r="B33" s="43" t="str"/>
-      <x:c r="C33" s="43" t="str"/>
-      <x:c r="D33" s="42" t="str"/>
-      <x:c r="E33" s="42" t="str"/>
-      <x:c r="F33" s="44" t="str"/>
-      <x:c r="G33" s="42" t="str"/>
-      <x:c r="H33" s="42" t="str"/>
-      <x:c r="I33" s="42" t="str"/>
-      <x:c r="J33" s="42" t="str"/>
+      <x:c r="A33" s="53" t="str"/>
+      <x:c r="B33" s="54" t="str"/>
+      <x:c r="C33" s="54" t="str"/>
+      <x:c r="D33" s="53" t="str"/>
+      <x:c r="E33" s="53" t="str"/>
+      <x:c r="F33" s="55" t="str"/>
+      <x:c r="G33" s="53" t="str"/>
+      <x:c r="H33" s="53" t="str"/>
+      <x:c r="I33" s="53" t="str"/>
+      <x:c r="J33" s="53" t="str"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="42" t="str"/>
-      <x:c r="B34" s="43" t="str"/>
-      <x:c r="C34" s="43" t="str"/>
-      <x:c r="D34" s="42" t="str"/>
-      <x:c r="E34" s="42" t="str"/>
-      <x:c r="F34" s="44" t="str"/>
-      <x:c r="G34" s="42" t="str"/>
-      <x:c r="H34" s="42" t="str"/>
-      <x:c r="I34" s="42" t="str"/>
-      <x:c r="J34" s="42" t="str"/>
+      <x:c r="A34" s="53" t="str"/>
+      <x:c r="B34" s="54" t="str"/>
+      <x:c r="C34" s="54" t="str"/>
+      <x:c r="D34" s="53" t="str"/>
+      <x:c r="E34" s="53" t="str"/>
+      <x:c r="F34" s="55" t="str"/>
+      <x:c r="G34" s="53" t="str"/>
+      <x:c r="H34" s="53" t="str"/>
+      <x:c r="I34" s="53" t="str"/>
+      <x:c r="J34" s="53" t="str"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="42" t="str"/>
-      <x:c r="B35" s="43" t="str"/>
-      <x:c r="C35" s="43" t="str"/>
-      <x:c r="D35" s="42" t="str"/>
-      <x:c r="E35" s="42" t="str"/>
-      <x:c r="F35" s="44" t="str"/>
-      <x:c r="G35" s="42" t="str"/>
-      <x:c r="H35" s="42" t="str"/>
-      <x:c r="I35" s="42" t="str"/>
-      <x:c r="J35" s="42" t="str"/>
+      <x:c r="A35" s="53" t="str"/>
+      <x:c r="B35" s="54" t="str"/>
+      <x:c r="C35" s="54" t="str"/>
+      <x:c r="D35" s="53" t="str"/>
+      <x:c r="E35" s="53" t="str"/>
+      <x:c r="F35" s="55" t="str"/>
+      <x:c r="G35" s="53" t="str"/>
+      <x:c r="H35" s="53" t="str"/>
+      <x:c r="I35" s="53" t="str"/>
+      <x:c r="J35" s="53" t="str"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="42" t="str"/>
-      <x:c r="B36" s="43" t="str"/>
-      <x:c r="C36" s="43" t="str"/>
-      <x:c r="D36" s="42" t="str"/>
-      <x:c r="E36" s="42" t="str"/>
-      <x:c r="F36" s="44" t="str"/>
-      <x:c r="G36" s="42" t="str"/>
-      <x:c r="H36" s="42" t="str"/>
-      <x:c r="I36" s="42" t="str"/>
-      <x:c r="J36" s="42" t="str"/>
+      <x:c r="A36" s="53" t="str"/>
+      <x:c r="B36" s="54" t="str"/>
+      <x:c r="C36" s="54" t="str"/>
+      <x:c r="D36" s="53" t="str"/>
+      <x:c r="E36" s="53" t="str"/>
+      <x:c r="F36" s="55" t="str"/>
+      <x:c r="G36" s="53" t="str"/>
+      <x:c r="H36" s="53" t="str"/>
+      <x:c r="I36" s="53" t="str"/>
+      <x:c r="J36" s="53" t="str"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="42" t="str"/>
-      <x:c r="B37" s="43" t="str"/>
-      <x:c r="C37" s="43" t="str"/>
-      <x:c r="D37" s="42" t="str"/>
-      <x:c r="E37" s="42" t="str"/>
-      <x:c r="F37" s="44" t="str"/>
-      <x:c r="G37" s="42" t="str"/>
-      <x:c r="H37" s="42" t="str"/>
-      <x:c r="I37" s="42" t="str"/>
-      <x:c r="J37" s="42" t="str"/>
+      <x:c r="A37" s="53" t="str"/>
+      <x:c r="B37" s="54" t="str"/>
+      <x:c r="C37" s="54" t="str"/>
+      <x:c r="D37" s="53" t="str"/>
+      <x:c r="E37" s="53" t="str"/>
+      <x:c r="F37" s="55" t="str"/>
+      <x:c r="G37" s="53" t="str"/>
+      <x:c r="H37" s="53" t="str"/>
+      <x:c r="I37" s="53" t="str"/>
+      <x:c r="J37" s="53" t="str"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="42" t="str"/>
-      <x:c r="B38" s="43" t="str"/>
-      <x:c r="C38" s="43" t="str"/>
-      <x:c r="D38" s="42" t="str"/>
-      <x:c r="E38" s="42" t="str"/>
-      <x:c r="F38" s="44" t="str"/>
-      <x:c r="G38" s="42" t="str"/>
-      <x:c r="H38" s="42" t="str"/>
-      <x:c r="I38" s="42" t="str"/>
-      <x:c r="J38" s="42" t="str"/>
+      <x:c r="A38" s="53" t="str"/>
+      <x:c r="B38" s="54" t="str"/>
+      <x:c r="C38" s="54" t="str"/>
+      <x:c r="D38" s="53" t="str"/>
+      <x:c r="E38" s="53" t="str"/>
+      <x:c r="F38" s="55" t="str"/>
+      <x:c r="G38" s="53" t="str"/>
+      <x:c r="H38" s="53" t="str"/>
+      <x:c r="I38" s="53" t="str"/>
+      <x:c r="J38" s="53" t="str"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="42" t="str"/>
-      <x:c r="B39" s="43" t="str"/>
-      <x:c r="C39" s="43" t="str"/>
-      <x:c r="D39" s="42" t="str"/>
-      <x:c r="E39" s="42" t="str"/>
-      <x:c r="F39" s="44" t="str"/>
-      <x:c r="G39" s="42" t="str"/>
-      <x:c r="H39" s="42" t="str"/>
-      <x:c r="I39" s="42" t="str"/>
-      <x:c r="J39" s="42" t="str"/>
+      <x:c r="A39" s="53" t="str"/>
+      <x:c r="B39" s="54" t="str"/>
+      <x:c r="C39" s="54" t="str"/>
+      <x:c r="D39" s="53" t="str"/>
+      <x:c r="E39" s="53" t="str"/>
+      <x:c r="F39" s="55" t="str"/>
+      <x:c r="G39" s="53" t="str"/>
+      <x:c r="H39" s="53" t="str"/>
+      <x:c r="I39" s="53" t="str"/>
+      <x:c r="J39" s="53" t="str"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="42" t="str"/>
-      <x:c r="B40" s="43" t="str"/>
-      <x:c r="C40" s="43" t="str"/>
-      <x:c r="D40" s="42" t="str"/>
-      <x:c r="E40" s="42" t="str"/>
-      <x:c r="F40" s="44" t="str"/>
-      <x:c r="G40" s="42" t="str"/>
-      <x:c r="H40" s="42" t="str"/>
-      <x:c r="I40" s="42" t="str"/>
-      <x:c r="J40" s="42" t="str"/>
+      <x:c r="A40" s="53" t="str"/>
+      <x:c r="B40" s="54" t="str"/>
+      <x:c r="C40" s="54" t="str"/>
+      <x:c r="D40" s="53" t="str"/>
+      <x:c r="E40" s="53" t="str"/>
+      <x:c r="F40" s="55" t="str"/>
+      <x:c r="G40" s="53" t="str"/>
+      <x:c r="H40" s="53" t="str"/>
+      <x:c r="I40" s="53" t="str"/>
+      <x:c r="J40" s="53" t="str"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="42" t="str"/>
-      <x:c r="B41" s="43" t="str"/>
-      <x:c r="C41" s="43" t="str"/>
-      <x:c r="D41" s="42" t="str"/>
-      <x:c r="E41" s="42" t="str"/>
-      <x:c r="F41" s="44" t="str"/>
-      <x:c r="G41" s="42" t="str"/>
-      <x:c r="H41" s="42" t="str"/>
-      <x:c r="I41" s="42" t="str"/>
-      <x:c r="J41" s="42" t="str"/>
+      <x:c r="A41" s="53" t="str"/>
+      <x:c r="B41" s="54" t="str"/>
+      <x:c r="C41" s="54" t="str"/>
+      <x:c r="D41" s="53" t="str"/>
+      <x:c r="E41" s="53" t="str"/>
+      <x:c r="F41" s="55" t="str"/>
+      <x:c r="G41" s="53" t="str"/>
+      <x:c r="H41" s="53" t="str"/>
+      <x:c r="I41" s="53" t="str"/>
+      <x:c r="J41" s="53" t="str"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="42" t="str"/>
-      <x:c r="B42" s="43" t="str"/>
-      <x:c r="C42" s="43" t="str"/>
-      <x:c r="D42" s="42" t="str"/>
-      <x:c r="E42" s="42" t="str"/>
-      <x:c r="F42" s="44" t="str"/>
-      <x:c r="G42" s="42" t="str"/>
-      <x:c r="H42" s="42" t="str"/>
-      <x:c r="I42" s="42" t="str"/>
-      <x:c r="J42" s="42" t="str"/>
+      <x:c r="A42" s="53" t="str"/>
+      <x:c r="B42" s="54" t="str"/>
+      <x:c r="C42" s="54" t="str"/>
+      <x:c r="D42" s="53" t="str"/>
+      <x:c r="E42" s="53" t="str"/>
+      <x:c r="F42" s="55" t="str"/>
+      <x:c r="G42" s="53" t="str"/>
+      <x:c r="H42" s="53" t="str"/>
+      <x:c r="I42" s="53" t="str"/>
+      <x:c r="J42" s="53" t="str"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="42" t="str"/>
-      <x:c r="B43" s="43" t="str"/>
-      <x:c r="C43" s="43" t="str"/>
-      <x:c r="D43" s="42" t="str"/>
-      <x:c r="E43" s="42" t="str"/>
-      <x:c r="F43" s="44" t="str"/>
-      <x:c r="G43" s="42" t="str"/>
-      <x:c r="H43" s="42" t="str"/>
-      <x:c r="I43" s="42" t="str"/>
-      <x:c r="J43" s="42" t="str"/>
+      <x:c r="A43" s="53" t="str"/>
+      <x:c r="B43" s="54" t="str"/>
+      <x:c r="C43" s="54" t="str"/>
+      <x:c r="D43" s="53" t="str"/>
+      <x:c r="E43" s="53" t="str"/>
+      <x:c r="F43" s="55" t="str"/>
+      <x:c r="G43" s="53" t="str"/>
+      <x:c r="H43" s="53" t="str"/>
+      <x:c r="I43" s="53" t="str"/>
+      <x:c r="J43" s="53" t="str"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="42" t="str"/>
-      <x:c r="B44" s="43" t="str"/>
-      <x:c r="C44" s="43" t="str"/>
-      <x:c r="D44" s="42" t="str"/>
-      <x:c r="E44" s="42" t="str"/>
-      <x:c r="F44" s="44" t="str"/>
-      <x:c r="G44" s="42" t="str"/>
-      <x:c r="H44" s="42" t="str"/>
-      <x:c r="I44" s="42" t="str"/>
-      <x:c r="J44" s="42" t="str"/>
+      <x:c r="A44" s="53" t="str"/>
+      <x:c r="B44" s="54" t="str"/>
+      <x:c r="C44" s="54" t="str"/>
+      <x:c r="D44" s="53" t="str"/>
+      <x:c r="E44" s="53" t="str"/>
+      <x:c r="F44" s="55" t="str"/>
+      <x:c r="G44" s="53" t="str"/>
+      <x:c r="H44" s="53" t="str"/>
+      <x:c r="I44" s="53" t="str"/>
+      <x:c r="J44" s="53" t="str"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="42" t="str"/>
-      <x:c r="B45" s="43" t="str"/>
-      <x:c r="C45" s="43" t="str"/>
-      <x:c r="D45" s="42" t="str"/>
-      <x:c r="E45" s="42" t="str"/>
-      <x:c r="F45" s="44" t="str"/>
-      <x:c r="G45" s="42" t="str"/>
-      <x:c r="H45" s="42" t="str"/>
-      <x:c r="I45" s="42" t="str"/>
-      <x:c r="J45" s="42" t="str"/>
+      <x:c r="A45" s="53" t="str"/>
+      <x:c r="B45" s="54" t="str"/>
+      <x:c r="C45" s="54" t="str"/>
+      <x:c r="D45" s="53" t="str"/>
+      <x:c r="E45" s="53" t="str"/>
+      <x:c r="F45" s="55" t="str"/>
+      <x:c r="G45" s="53" t="str"/>
+      <x:c r="H45" s="53" t="str"/>
+      <x:c r="I45" s="53" t="str"/>
+      <x:c r="J45" s="53" t="str"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="42" t="str"/>
-      <x:c r="B46" s="43" t="str"/>
-      <x:c r="C46" s="43" t="str"/>
-      <x:c r="D46" s="42" t="str"/>
-      <x:c r="E46" s="42" t="str"/>
-      <x:c r="F46" s="44" t="str"/>
-      <x:c r="G46" s="42" t="str"/>
-      <x:c r="H46" s="42" t="str"/>
-      <x:c r="I46" s="42" t="str"/>
-      <x:c r="J46" s="42" t="str"/>
+      <x:c r="A46" s="53" t="str"/>
+      <x:c r="B46" s="54" t="str"/>
+      <x:c r="C46" s="54" t="str"/>
+      <x:c r="D46" s="53" t="str"/>
+      <x:c r="E46" s="53" t="str"/>
+      <x:c r="F46" s="55" t="str"/>
+      <x:c r="G46" s="53" t="str"/>
+      <x:c r="H46" s="53" t="str"/>
+      <x:c r="I46" s="53" t="str"/>
+      <x:c r="J46" s="53" t="str"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="42" t="str"/>
-      <x:c r="B47" s="43" t="str"/>
-      <x:c r="C47" s="43" t="str"/>
-      <x:c r="D47" s="42" t="str"/>
-      <x:c r="E47" s="42" t="str"/>
-      <x:c r="F47" s="44" t="str"/>
-      <x:c r="G47" s="42" t="str"/>
-      <x:c r="H47" s="42" t="str"/>
-      <x:c r="I47" s="42" t="str"/>
-      <x:c r="J47" s="42" t="str"/>
+      <x:c r="A47" s="53" t="str"/>
+      <x:c r="B47" s="54" t="str"/>
+      <x:c r="C47" s="54" t="str"/>
+      <x:c r="D47" s="53" t="str"/>
+      <x:c r="E47" s="53" t="str"/>
+      <x:c r="F47" s="55" t="str"/>
+      <x:c r="G47" s="53" t="str"/>
+      <x:c r="H47" s="53" t="str"/>
+      <x:c r="I47" s="53" t="str"/>
+      <x:c r="J47" s="53" t="str"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="42" t="str"/>
-      <x:c r="B48" s="43" t="str"/>
-      <x:c r="C48" s="43" t="str"/>
-      <x:c r="D48" s="42" t="str"/>
-      <x:c r="E48" s="42" t="str"/>
-      <x:c r="F48" s="44" t="str"/>
-      <x:c r="G48" s="42" t="str"/>
-      <x:c r="H48" s="42" t="str"/>
-      <x:c r="I48" s="42" t="str"/>
-      <x:c r="J48" s="42" t="str"/>
+      <x:c r="A48" s="53" t="str"/>
+      <x:c r="B48" s="54" t="str"/>
+      <x:c r="C48" s="54" t="str"/>
+      <x:c r="D48" s="53" t="str"/>
+      <x:c r="E48" s="53" t="str"/>
+      <x:c r="F48" s="55" t="str"/>
+      <x:c r="G48" s="53" t="str"/>
+      <x:c r="H48" s="53" t="str"/>
+      <x:c r="I48" s="53" t="str"/>
+      <x:c r="J48" s="53" t="str"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="42" t="str"/>
-      <x:c r="B49" s="43" t="str"/>
-      <x:c r="C49" s="43" t="str"/>
-      <x:c r="D49" s="42" t="str"/>
-      <x:c r="E49" s="42" t="str"/>
-      <x:c r="F49" s="44" t="str"/>
-      <x:c r="G49" s="42" t="str"/>
-      <x:c r="H49" s="42" t="str"/>
-      <x:c r="I49" s="42" t="str"/>
-      <x:c r="J49" s="42" t="str"/>
+      <x:c r="A49" s="53" t="str"/>
+      <x:c r="B49" s="54" t="str"/>
+      <x:c r="C49" s="54" t="str"/>
+      <x:c r="D49" s="53" t="str"/>
+      <x:c r="E49" s="53" t="str"/>
+      <x:c r="F49" s="55" t="str"/>
+      <x:c r="G49" s="53" t="str"/>
+      <x:c r="H49" s="53" t="str"/>
+      <x:c r="I49" s="53" t="str"/>
+      <x:c r="J49" s="53" t="str"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="42" t="str"/>
-      <x:c r="B50" s="43" t="str"/>
-      <x:c r="C50" s="43" t="str"/>
-      <x:c r="D50" s="42" t="str"/>
-      <x:c r="E50" s="42" t="str"/>
-      <x:c r="F50" s="44" t="str"/>
-      <x:c r="G50" s="42" t="str"/>
-      <x:c r="H50" s="42" t="str"/>
-      <x:c r="I50" s="42" t="str"/>
-      <x:c r="J50" s="42" t="str"/>
+      <x:c r="A50" s="53" t="str"/>
+      <x:c r="B50" s="54" t="str"/>
+      <x:c r="C50" s="54" t="str"/>
+      <x:c r="D50" s="53" t="str"/>
+      <x:c r="E50" s="53" t="str"/>
+      <x:c r="F50" s="55" t="str"/>
+      <x:c r="G50" s="53" t="str"/>
+      <x:c r="H50" s="53" t="str"/>
+      <x:c r="I50" s="53" t="str"/>
+      <x:c r="J50" s="53" t="str"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="42" t="str"/>
-      <x:c r="B51" s="43" t="str"/>
-      <x:c r="C51" s="43" t="str"/>
-      <x:c r="D51" s="42" t="str"/>
-      <x:c r="E51" s="42" t="str"/>
-      <x:c r="F51" s="44" t="str"/>
-      <x:c r="G51" s="42" t="str"/>
-      <x:c r="H51" s="42" t="str"/>
-      <x:c r="I51" s="42" t="str"/>
-      <x:c r="J51" s="42" t="str"/>
+      <x:c r="A51" s="53" t="str"/>
+      <x:c r="B51" s="54" t="str"/>
+      <x:c r="C51" s="54" t="str"/>
+      <x:c r="D51" s="53" t="str"/>
+      <x:c r="E51" s="53" t="str"/>
+      <x:c r="F51" s="55" t="str"/>
+      <x:c r="G51" s="53" t="str"/>
+      <x:c r="H51" s="53" t="str"/>
+      <x:c r="I51" s="53" t="str"/>
+      <x:c r="J51" s="53" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1064,302 +1127,306 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="28" t="str">
+      <x:c r="A1" s="61" t="str">
         <x:v>走向・傾斜マップ Excel入力テンプレート</x:v>
       </x:c>
-      <x:c r="B1" s="28" t="str"/>
+      <x:c r="B1" s="61" t="str"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="29" t="str">
+      <x:c r="A2" s="63" t="str">
         <x:v>項目</x:v>
       </x:c>
-      <x:c r="B2" s="29" t="str">
+      <x:c r="B2" s="63" t="str">
         <x:v>記入方法</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="A3" s="58" t="str">
         <x:v>地点番号</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="str">
+      <x:c r="B3" s="58" t="str">
         <x:v>任意の識別名．例．F001，MUR-01</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
+      <x:c r="A4" s="58" t="str">
         <x:v>緯度</x:v>
       </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="B4" s="58" t="str">
         <x:v>10進数．例．34.910884</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="58" t="str">
         <x:v>経度</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="B5" s="58" t="str">
         <x:v>10進数．例．139.824167</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11" t="str">
+      <x:c r="A6" s="58" t="str">
         <x:v>走向</x:v>
       </x:c>
-      <x:c r="B6" s="11" t="str">
+      <x:c r="B6" s="58" t="str">
         <x:v>例．N30E，N30°E，030</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11" t="str">
+      <x:c r="A7" s="58" t="str">
         <x:v>傾斜</x:v>
       </x:c>
-      <x:c r="B7" s="11" t="str">
+      <x:c r="B7" s="58" t="str">
         <x:v>例．45SE，45°NW</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11" t="str">
+      <x:c r="A8" s="58" t="str">
         <x:v>測定日</x:v>
       </x:c>
-      <x:c r="B8" s="11" t="str">
+      <x:c r="B8" s="58" t="str">
         <x:v>Excelの日付または yyyy-mm-dd．空欄可</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
+      <x:c r="A9" s="58" t="str">
         <x:v>岩種・地層名</x:v>
       </x:c>
-      <x:c r="B9" s="11" t="str">
+      <x:c r="B9" s="58" t="str">
         <x:v>自由入力．例．シルト岩，布良層</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
+      <x:c r="A10" s="58" t="str">
         <x:v>面・構造</x:v>
       </x:c>
-      <x:c r="B10" s="11" t="str">
+      <x:c r="B10" s="58" t="str">
         <x:v>自由入力．例．層理面，亀裂，断層面，層面すべり面</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
+      <x:c r="A11" s="58" t="str">
         <x:v>補足情報</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="str">
+      <x:c r="B11" s="58" t="str">
         <x:v>自由入力．写真番号，露頭状態，観察事項など</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="str"/>
-      <x:c r="B12" s="11" t="str"/>
+      <x:c r="A12" s="58" t="str"/>
+      <x:c r="B12" s="58" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="29" t="str">
+      <x:c r="A13" s="63" t="str">
         <x:v>記入例</x:v>
       </x:c>
-      <x:c r="B13" s="29" t="str"/>
+      <x:c r="B13" s="63" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11" t="str">
+      <x:c r="A14" s="58" t="str">
         <x:v>地点番号</x:v>
       </x:c>
-      <x:c r="B14" s="11" t="str">
+      <x:c r="B14" s="58" t="str">
         <x:v>F001</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11" t="str">
+      <x:c r="A15" s="58" t="str">
         <x:v>緯度</x:v>
       </x:c>
-      <x:c r="B15" s="11" t="n">
+      <x:c r="B15" s="58" t="n">
         <x:v>34.910884</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11" t="str">
+      <x:c r="A16" s="58" t="str">
         <x:v>経度</x:v>
       </x:c>
-      <x:c r="B16" s="11" t="n">
+      <x:c r="B16" s="58" t="n">
         <x:v>139.824167</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11" t="str">
+      <x:c r="A17" s="58" t="str">
         <x:v>走向</x:v>
       </x:c>
-      <x:c r="B17" s="11" t="str">
+      <x:c r="B17" s="58" t="str">
         <x:v>N30E</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11" t="str">
+      <x:c r="A18" s="58" t="str">
         <x:v>傾斜</x:v>
       </x:c>
-      <x:c r="B18" s="11" t="str">
+      <x:c r="B18" s="58" t="str">
         <x:v>45SE</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11" t="str">
+      <x:c r="A19" s="58" t="str">
         <x:v>測定日</x:v>
       </x:c>
-      <x:c r="B19" s="11" t="str">
+      <x:c r="B19" s="58" t="str">
         <x:v>2026-09-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11" t="str">
+      <x:c r="A20" s="58" t="str">
         <x:v>岩種・地層名</x:v>
       </x:c>
-      <x:c r="B20" s="11" t="str">
+      <x:c r="B20" s="58" t="str">
         <x:v>シルト岩／布良層</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="11" t="str">
+      <x:c r="A21" s="58" t="str">
         <x:v>面・構造</x:v>
       </x:c>
-      <x:c r="B21" s="11" t="str">
+      <x:c r="B21" s="58" t="str">
         <x:v>層理面</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="11" t="str">
+      <x:c r="A22" s="58" t="str">
         <x:v>補足情報</x:v>
       </x:c>
-      <x:c r="B22" s="11" t="str">
+      <x:c r="B22" s="58" t="str">
         <x:v>写真 IMG_3241．層理面は比較的平滑．</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="34" t="str">
+      <x:c r="A23" s="64" t="str">
         <x:v>地点番号による既存ポイント対応</x:v>
       </x:c>
-      <x:c r="B23" s="34" t="str"/>
+      <x:c r="B23" s="64" t="str"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="11" t="str">
+      <x:c r="A24" s="58" t="str">
         <x:v>既存ポイントに反映する場合</x:v>
       </x:c>
-      <x:c r="B24" s="11" t="str">
+      <x:c r="B24" s="58" t="str">
         <x:v>Webアプリ上の地点番号とExcelの地点番号を同じにしてください．緯度・経度は空欄でも構いません．</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="11" t="str">
+      <x:c r="A25" s="58" t="str">
         <x:v>緯度・経度を入力した場合</x:v>
       </x:c>
-      <x:c r="B25" s="11" t="str">
+      <x:c r="B25" s="58" t="str">
         <x:v>同じ地点番号の既存ポイントがある場合，そのポイントの座標もExcelの値へ更新します．</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="11" t="str">
+      <x:c r="A26" s="58" t="str">
         <x:v>新規ポイントを作る場合</x:v>
       </x:c>
-      <x:c r="B26" s="11" t="str">
+      <x:c r="B26" s="58" t="str">
         <x:v>地点番号に加えて緯度・経度を入力してください．一致する既存ポイントがない場合，新規ポイントとして作成します．</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="11" t="str">
+      <x:c r="A27" s="58" t="str">
         <x:v>対応先なし＋座標なし</x:v>
       </x:c>
-      <x:c r="B27" s="11" t="str">
+      <x:c r="B27" s="58" t="str">
         <x:v>既存ポイントが見つからず，緯度・経度も空欄の場合はエラーになります．</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="11" t="str">
+      <x:c r="A28" s="58" t="str">
         <x:v>おすすめ運用</x:v>
       </x:c>
-      <x:c r="B28" s="11" t="str">
+      <x:c r="B28" s="58" t="str">
         <x:v>先にGPXや地図クリックで位置ポイントを作成し，地点番号を合わせたExcelで走向・傾斜や補足情報を一括反映します．</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="11" t="str">
+      <x:c r="A29" s="58" t="str">
         <x:v>例</x:v>
       </x:c>
-      <x:c r="B29" s="11" t="str">
+      <x:c r="B29" s="58" t="str">
         <x:v>地図側 F023 ＋ Excel側 F023 → F023の既存ポイントへ情報を反映します．</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="60"/>
+      <x:c r="B30" s="60"/>
+    </x:row>
     <x:row r="31">
-      <x:c r="A31" s="50" t="str">
+      <x:c r="A31" s="64" t="str">
         <x:v>おすすめの作業フロー</x:v>
       </x:c>
-      <x:c r="B31" s="50" t="str"/>
+      <x:c r="B31" s="64" t="str"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="11" t="str">
+      <x:c r="A32" s="58" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B32" s="11" t="str">
+      <x:c r="B32" s="58" t="str">
         <x:v>WebアプリでGPXや地図クリックから位置ポイントを作成し，地点番号を付けます．</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="11" t="str">
+      <x:c r="A33" s="58" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B33" s="11" t="str">
+      <x:c r="B33" s="58" t="str">
         <x:v>Webアプリの「現在のポイントから入力用Excelを作成」を押します．</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="11" t="str">
+      <x:c r="A34" s="58" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B34" s="11" t="str">
+      <x:c r="B34" s="58" t="str">
         <x:v>地点番号と緯度・経度が入ったExcelがダウンロードされます．</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="11" t="str">
+      <x:c r="A35" s="58" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B35" s="11" t="str">
+      <x:c r="B35" s="58" t="str">
         <x:v>Excelで走向，傾斜，測定日，岩種・地層名，面・構造，色区分，補足情報を入力します．</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="11" t="str">
+      <x:c r="A36" s="58" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B36" s="11" t="str">
+      <x:c r="B36" s="58" t="str">
         <x:v>ExcelをWebアプリへ読み込むと，地点番号が一致する既存ポイントへ反映されます．</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="11" t="str">
+      <x:c r="A37" s="58" t="str">
         <x:v>色区分</x:v>
       </x:c>
-      <x:c r="B37" s="11" t="str">
+      <x:c r="B37" s="58" t="str">
         <x:v>「色定義」シートで色区分名とHEX色を自由に定義できます．</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="11" t="str">
+      <x:c r="A38" s="58" t="str">
         <x:v>色の例</x:v>
       </x:c>
-      <x:c r="B38" s="11" t="str">
+      <x:c r="B38" s="58" t="str">
         <x:v>黒 #111111，赤 #d62728，青 #1f77b4</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="11" t="str">
+      <x:c r="A39" s="58" t="str">
         <x:v>地点番号</x:v>
       </x:c>
-      <x:c r="B39" s="11" t="str">
+      <x:c r="B39" s="58" t="str">
         <x:v>既存ポイントとの対応キーなので，意図なく変更しないことを推奨します．</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="11" t="str">
+      <x:c r="A40" s="58" t="str">
         <x:v>座標</x:v>
       </x:c>
-      <x:c r="B40" s="11" t="str">
+      <x:c r="B40" s="58" t="str">
         <x:v>既存ポイントへ反映するだけなら，Excel側の緯度・経度は空欄でも構いません．</x:v>
       </x:c>
     </x:row>
@@ -1382,104 +1449,104 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="46" t="str">
+      <x:c r="A1" s="61" t="str">
         <x:v>色区分</x:v>
       </x:c>
-      <x:c r="B1" s="46" t="str">
+      <x:c r="B1" s="61" t="str">
         <x:v>色(HEX)</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="11" t="str">
+      <x:c r="A2" s="58" t="str">
         <x:v>標準</x:v>
       </x:c>
-      <x:c r="B2" s="11" t="str">
+      <x:c r="B2" s="58" t="str">
         <x:v>#111111</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="11" t="str">
+      <x:c r="A3" s="58" t="str">
         <x:v>層理面</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="str">
+      <x:c r="B3" s="58" t="str">
         <x:v>#111111</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="11" t="str">
+      <x:c r="A4" s="58" t="str">
         <x:v>亀裂</x:v>
       </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="B4" s="58" t="str">
         <x:v>#d62728</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="11" t="str">
+      <x:c r="A5" s="58" t="str">
         <x:v>層面すべり面</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="B5" s="58" t="str">
         <x:v>#1f77b4</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="11"/>
-      <x:c r="B6" s="11"/>
+      <x:c r="A6" s="58"/>
+      <x:c r="B6" s="58"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="11"/>
-      <x:c r="B7" s="11"/>
+      <x:c r="A7" s="58"/>
+      <x:c r="B7" s="58"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="11"/>
-      <x:c r="B8" s="11"/>
+      <x:c r="A8" s="58"/>
+      <x:c r="B8" s="58"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11"/>
-      <x:c r="B9" s="11"/>
+      <x:c r="A9" s="58"/>
+      <x:c r="B9" s="58"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11"/>
-      <x:c r="B10" s="11"/>
+      <x:c r="A10" s="58"/>
+      <x:c r="B10" s="58"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11"/>
-      <x:c r="B11" s="11"/>
+      <x:c r="A11" s="58"/>
+      <x:c r="B11" s="58"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11"/>
-      <x:c r="B12" s="11"/>
+      <x:c r="A12" s="58"/>
+      <x:c r="B12" s="58"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11"/>
-      <x:c r="B13" s="11"/>
+      <x:c r="A13" s="58"/>
+      <x:c r="B13" s="58"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="11"/>
+      <x:c r="A14" s="58"/>
+      <x:c r="B14" s="58"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="11"/>
-      <x:c r="B15" s="11"/>
+      <x:c r="A15" s="58"/>
+      <x:c r="B15" s="58"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="11"/>
-      <x:c r="B16" s="11"/>
+      <x:c r="A16" s="58"/>
+      <x:c r="B16" s="58"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="11"/>
-      <x:c r="B17" s="11"/>
+      <x:c r="A17" s="58"/>
+      <x:c r="B17" s="58"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="11"/>
-      <x:c r="B18" s="11"/>
+      <x:c r="A18" s="58"/>
+      <x:c r="B18" s="58"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="11"/>
-      <x:c r="B19" s="11"/>
+      <x:c r="A19" s="58"/>
+      <x:c r="B19" s="58"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="11"/>
-      <x:c r="B20" s="11"/>
+      <x:c r="A20" s="58"/>
+      <x:c r="B20" s="58"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
